--- a/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>KAR</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>391300</v>
+      </c>
+      <c r="E8" s="3">
         <v>416300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>416900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>420600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>372800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>393000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>753600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>369400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>357700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>347100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>745800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>369800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>529600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>593600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1064500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>645500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>671300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>701900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>719100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>689600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>593800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>612400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>956600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>950500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>890400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>843000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>858000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>866600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>859500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>789600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>204800</v>
+      </c>
+      <c r="E9" s="3">
         <v>216000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>222600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>224200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>202000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>209600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>422700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>210800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>194200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>185700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>412600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>203800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>325400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>329700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>629700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>394600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>394900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>410900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>417400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>393900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>332300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>330700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>531300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>535000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>525100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>479200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>481700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>501200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>534100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>459500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>186500</v>
+      </c>
+      <c r="E10" s="3">
         <v>200300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>194300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>196400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>170800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>183400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>330900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>158600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>163500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>161400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>333200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>166000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>204200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>263900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>434800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>250900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>276400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>291000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>301700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>295700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>261500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>281700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>425300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>415500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>365300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>363800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>376300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>365400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>325400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>330100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,70 +1298,73 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>16100</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>233200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>9300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7700</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-44400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>15700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>29800</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>2200</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1353,121 +1372,127 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>27500</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>1400</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E15" s="3">
         <v>26400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>23000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>24000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>51900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>26000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>28200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>27400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>54300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>26900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>50600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>46500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>94200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>47700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>50100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>46400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>47900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>44300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>42600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>41400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>66900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>70300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>69400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>66200</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>64500</v>
       </c>
       <c r="AD15" s="3">
         <v>64500</v>
       </c>
       <c r="AE15" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AF15" s="3">
         <v>64700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>350000</v>
+      </c>
+      <c r="E17" s="3">
         <v>349800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>593800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>366200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>285300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>352300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>725300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>355700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>280200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>322300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>696300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>349200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>515700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>507200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1028400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>604700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>609700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>618400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>628500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>613400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>523600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>526800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>781000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>792700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>767000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>701100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>728300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>723100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>749000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>666300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E18" s="3">
         <v>66500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-176900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>54400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>87500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>40700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>28300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>77500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>49500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>20600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>86400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>40800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>61600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>83500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>90600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>76200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>70200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>85600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>175600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>157800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>123400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>141900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>129700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>143500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>110500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>123300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-52400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>50100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>60900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>23000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E21" s="3">
         <v>91200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-147500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>81300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>119200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>63800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>75000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>38500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>53300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>42700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>153900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>108400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>60600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>134000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>131000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>90500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>114200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>131900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>139200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>122100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>111500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>130200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>196400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>232900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>215800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>208300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>195300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>208000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>174900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E22" s="3">
         <v>39400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>38800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>38300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>32300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>51500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>32000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>31900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>61800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>30800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>30500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>29500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>68900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>38000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>39500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>37900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>55200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>56000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>52000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>49200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>49900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>46200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>43300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>41600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>39700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>40200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>38000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>36300</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E23" s="3">
         <v>25400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-213100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>59800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>37800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>50700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>58000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-32100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>47600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>16900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>39600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>128400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>116400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>103100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>100500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>91100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>103300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>72200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>86200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E24" s="3">
         <v>12700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-19300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>17900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-14600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-22100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>26900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>13200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>35200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>26400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>37700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>33900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>34100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>26700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E26" s="3">
         <v>12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-193800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>41900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>26200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>47100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-29500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>34400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>15100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>30900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>93200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>90000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>81200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>62800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>57200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>69200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>45500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-204900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-24800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-37300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>34400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>30900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>93200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>90000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>81200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>62800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>57200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>69200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>45500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,13 +2600,16 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2558,32 +2618,32 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-4800</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-6300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>223700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>8100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-10100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>25900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>51500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>24700</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
@@ -2594,34 +2654,34 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>4500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>28200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>62500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>52200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>46600</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E32" s="3">
         <v>1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>52400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-50100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-60900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-204900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>198900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>52100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>55600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>77800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>67300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>77500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>93200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>90000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>172800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>62800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>57200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>69200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>45500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-204900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>198900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>52100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>55600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>77800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>67300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>77500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>93200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>90000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>172800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>62800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>57200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>69200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>45500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E41" s="3">
         <v>110300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>242400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>219600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>225700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>148700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>804400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>134200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>177600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>631900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>621600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>759000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>752100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1276700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>968500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>293100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>507600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>508600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>233000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>265600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>277100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>455100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>369800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>330800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>317200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>432100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>530400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>188000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>201800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>323100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,100 +3625,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2573800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2698100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2712000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2725700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2665800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2953500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3085800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3168100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2887300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2733000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2634100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2618200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2256200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2216900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2108600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2173900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2557700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2605800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2648400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2937300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2455400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2817100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2785200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2883500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2625100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2558300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2435000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2521400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2463100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2457400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,192 +3815,201 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>174600</v>
+      </c>
+      <c r="E45" s="3">
         <v>132400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>129700</v>
       </c>
       <c r="F45" s="3">
         <v>129700</v>
       </c>
       <c r="G45" s="3">
+        <v>129700</v>
+      </c>
+      <c r="H45" s="3">
         <v>130900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>106300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2202700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>326900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>163300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>158900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>148300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>166900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>181000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>174000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>245900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>179200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>143300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>167500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>257300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>581700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>199400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>206300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>196800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>195100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>183700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>170700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>178200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>176300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>153800</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2841900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2940800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3084100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3075000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3022400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3202900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3996500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5505000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3391800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3528200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3414600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3525500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3175200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3674600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3251100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2712900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3244500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3257700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3048900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3460200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3314200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3471600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3361300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3411100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3137400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3174100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3136100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2887600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2841200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2934300</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,192 +4100,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>245700</v>
+      </c>
+      <c r="E48" s="3">
         <v>192800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>198700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>203000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>208400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>217200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>228800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>235400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>238200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>901300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>918600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>921200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>940500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>940100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>936800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>952700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>973100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>969500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>965500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1770800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2463800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>912000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>904500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>909600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>908200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>870500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>841300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>837500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>842500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>827700</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1588800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1547800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1566100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1825300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1831700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1824700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1850400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1985400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2000400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2673700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2696600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2617800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2641700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2251200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2261100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2300400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2328100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2324200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2336500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3052100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2535200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2878900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2889400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2909200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2917900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2818400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2837800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2814200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2838100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2787600</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E52" s="3">
         <v>47900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>48500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>44600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>57300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>56500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>50300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>66600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1820300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>67000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>88500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>95700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>40800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>44000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>45000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>33700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>35500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>28300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>41000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1084300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>38100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>38900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>36300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>42600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>41500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>40900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>35800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4726300</v>
+      </c>
+      <c r="E54" s="3">
         <v>4729300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4897400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5147900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5119800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5301300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6126000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7792400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7450700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7170200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7118300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7160200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6798200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6909900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6494000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5999700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6581200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6579700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6377800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8324100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7206200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7300600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7194100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7266200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6984300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6905600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6856700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6580200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6557600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6586400</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>556600</v>
+      </c>
+      <c r="E57" s="3">
         <v>646400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>625700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>683800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>551200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>645600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>736100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>833500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>785300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1070200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1074500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1118100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>688900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>938100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>983800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>354300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>704600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>718500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>847100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>997800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>691300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>870300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>874400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>942700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>682700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>754600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>735500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>786500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>648500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>700300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>155500</v>
+      </c>
+      <c r="E58" s="3">
         <v>42300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>187900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>225800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>290600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>283600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>760900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1034000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>19900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>22700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>30400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>24300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>26400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>26900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>27000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>42100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>39000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>105500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>148200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>13100</v>
-      </c>
-      <c r="X58" s="3">
-        <v>17700</v>
       </c>
       <c r="Y58" s="3">
         <v>17700</v>
       </c>
       <c r="Z58" s="3">
+        <v>17700</v>
+      </c>
+      <c r="AA58" s="3">
         <v>16800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>12400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>16800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>17700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>38000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>105200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1766700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1820000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1832600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1756800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1801400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1891200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2050900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2614300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2374000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1667400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1586100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1507500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1537400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1390000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>998600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1637500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1771000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1758700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1715800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1799600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1920400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1736900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1672100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1668400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1694100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1576200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1509700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1509100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1581300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1558900</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2478800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2508700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2646200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2666400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2643200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2820400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3547900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4481800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3009300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2756700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2683300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2656000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2250600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2354500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2009300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2018800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2517700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2516200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2668400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2945600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2624800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2624900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2564200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2627900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2389200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2347600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2262900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2333600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2335000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2283900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>202400</v>
+      </c>
+      <c r="E61" s="3">
         <v>201400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>201000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>206000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>206200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>194700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>190700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>939800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1852700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1850700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1851800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1852800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1853800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1854800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1856900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1860100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1875300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1877600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1403800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2676000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2654300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2657600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2660900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2664300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2667700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2671000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2675200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2360500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2365100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2371800</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>105600</v>
+      </c>
+      <c r="E62" s="3">
         <v>101100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>103300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>137100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>139600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>139300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>146000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>253300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>484800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>499700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>511900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>504100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>528200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>553600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>545100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>549000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>538000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>550100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>553000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1200000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>462900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>456600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>456500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>453900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>442500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>484300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>456800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>455700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>460200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>452900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2786800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2811200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2950500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3009500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2989000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3154400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3884600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5674900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5346800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5107100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5047000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5012900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4632600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4762900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4411300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4427900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4931000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4943900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4625200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6821600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5742000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5739100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5681600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5746100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5499400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5502900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5394900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5149800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5160300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5108600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5870,32 +6037,32 @@
         <v>612500</v>
       </c>
       <c r="J70" s="3">
+        <v>612500</v>
+      </c>
+      <c r="K70" s="3">
         <v>601600</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>590900</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>580400</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>570000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>559800</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>549800</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>540000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>528200</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>624400</v>
+      </c>
+      <c r="E72" s="3">
         <v>621200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>619600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>824500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>822900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>796900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>813800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>614600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>625700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>631100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>642500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>641200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>600700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>627800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>592500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>624800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>651000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>655700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>644900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>422900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>392300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>371500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>341100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>295000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>257000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>131300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>111800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>98600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>74100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1327000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1305600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1334400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1525900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1518300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1534400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1628900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1515900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1513000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1482700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1501300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1587500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1615800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1607000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1554500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1571800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1650200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1635800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1752600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1502500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1464200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1561500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1512500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1520100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1484900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1402700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1430400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1397300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1477800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-204900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>198900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>52100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>55600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>77800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>67300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>77500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>93200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>90000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>172800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>62800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>57200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>69200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>45500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E83" s="3">
         <v>26400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>51900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>44700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>92400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>47000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>50600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>46500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>94200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>47700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>50100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>46400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>26100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>66100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>67100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>65600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>66900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>70300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>69400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>66200</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>64500</v>
       </c>
       <c r="AD83" s="3">
         <v>64500</v>
       </c>
       <c r="AE83" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AF83" s="3">
         <v>64700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E89" s="3">
         <v>73600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>46400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>96100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-125300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-326900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-86100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>73300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>59800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>295700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>164500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-47500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>163000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>268900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-49200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>94200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>130300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>223800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>93700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>164000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>199100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>234400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>152300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>100900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>114000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>231900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>142000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>87100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-46700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-29600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-34000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-49200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-46100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-32300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-48600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-34700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-74400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-73200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-161500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="E94" s="3">
         <v>12400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>164400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>109800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1873200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-258500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-803600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-89300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-325700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-79200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-590200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-222300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>485900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>116700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-47700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-98400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-150300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-156000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-147100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-68600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-74000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-91500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-109600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-134400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-99800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7930,55 +8163,58 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-49000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-24500</v>
       </c>
       <c r="S96" s="3">
         <v>-24500</v>
       </c>
       <c r="T96" s="3">
-        <v>0</v>
+        <v>-24500</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-93300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-46500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-47100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-47000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-47200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-43300</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-43900</v>
       </c>
       <c r="AC96" s="3">
         <v>-43900</v>
       </c>
       <c r="AD96" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-43700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-40100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-40000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-116500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-81900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-618100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-911100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>298700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>273100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>50600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-113300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-88700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>105900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>368800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-279900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-197200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-23300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>247100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-51700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-18300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-114400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-48200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-115700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-41800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-34500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-110900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>174200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-136400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-59300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-13900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-21300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>12700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-17300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-23700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>5800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-15500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>8500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-120400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-25900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>100100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-654900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>629100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-42900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-455600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-136900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-519100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>312900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>457600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-153400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>29000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>275200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>26800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-74800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-113000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>87200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>39100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-115600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-98000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>342300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-121300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>8400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>KAR</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>416300</v>
+      </c>
+      <c r="E8" s="3">
         <v>391300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>416300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>416900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>420600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>372800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>393000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>753600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>369400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>357700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>347100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>745800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>369800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>529600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>593600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1064500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>645500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>671300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>701900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>719100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>689600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>593800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>612400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>956600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>950500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>890400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>843000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>858000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>866600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>859500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>789600</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>213900</v>
+      </c>
+      <c r="E9" s="3">
         <v>204800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>216000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>222600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>224200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>202000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>209600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>422700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>210800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>194200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>185700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>412600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>203800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>325400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>329700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>629700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>394600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>394900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>410900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>417400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>393900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>332300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>330700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>531300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>535000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>525100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>479200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>481700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>501200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>534100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>459500</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>202400</v>
+      </c>
+      <c r="E10" s="3">
         <v>186500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>194300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>196400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>170800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>183400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>330900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>158600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>163500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>161400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>333200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>166000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>204200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>263900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>434800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>250900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>276400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>291000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>301700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>295700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>261500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>281700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>425300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>415500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>365300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>363800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>376300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>365400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>325400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>330100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,73 +1318,76 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>16100</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>233200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7700</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-44400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>15700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>29800</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2200</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1375,124 +1395,130 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>27500</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>1400</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E15" s="3">
         <v>25300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>26800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>23000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>51900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>26000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>28200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>27400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>54300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>26900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>50600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>46500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>94200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>47700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>50100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>46400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>47900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>44300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>42600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>41400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>66900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>70300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>69400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>66200</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>64500</v>
       </c>
       <c r="AE15" s="3">
         <v>64500</v>
       </c>
       <c r="AF15" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AG15" s="3">
         <v>64700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>350000</v>
+        <v>346900</v>
       </c>
       <c r="E17" s="3">
+        <v>333200</v>
+      </c>
+      <c r="F17" s="3">
         <v>349800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>593800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>366200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>285300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>352300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>725300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>355700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>280200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>322300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>696300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>349200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>515700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>507200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1028400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>604700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>609700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>618400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>628500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>613400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>523600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>526800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>781000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>792700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>767000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>701100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>728300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>723100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>749000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>666300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>41300</v>
+        <v>69400</v>
       </c>
       <c r="E18" s="3">
+        <v>58100</v>
+      </c>
+      <c r="F18" s="3">
         <v>66500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-176900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>54400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>87500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>40700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>77500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>49500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>86400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>36100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>40800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>61600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>83500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>90600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>76200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>70200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>85600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>175600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>157800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>123400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>141900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>129700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>143500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>110500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>123300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>19200</v>
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-52400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>50100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>60900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>23000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E21" s="3">
         <v>85800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>91200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-147500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>81300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>119200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>63800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>75000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>38500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>53300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>42700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>153900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>108400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>60600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>134000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>131000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>90500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>114200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>131900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>139200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>122100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>111500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>130200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>196400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>232900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>215800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>208300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>195300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>208000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>174900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E22" s="3">
         <v>39300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>39400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>38800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>38300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>35400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>32300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>51500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>32000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>31900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>61800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>30800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>30500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>29500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>68900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>38000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>39500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>37900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>55200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>56000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>52000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>49200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>49900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>46200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>43300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>41600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>39700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>40200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>38000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>36300</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E23" s="3">
         <v>21200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>25400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-213100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>59800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>37800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>50700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>58000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-32100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>24600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>47600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>16900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>39600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>128400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>116400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>103100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>100500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>91100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>103300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>72200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>86200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E24" s="3">
         <v>7600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-19300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>17900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-14600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-22100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>26900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>24500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>35200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>26400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>37700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>33900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>34100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>26700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E26" s="3">
         <v>13600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-193800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>41900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>47100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-29500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>34400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>27400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>15300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>30900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>93200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>90000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>81200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>62800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>57200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>69200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>45500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E27" s="3">
         <v>2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-204900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>23800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-37300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>30000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-24200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>34400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>27400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>30900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>93200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>90000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>81200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>62800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>57200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>69200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>45500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,17 +2661,20 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>700</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -2621,32 +2682,32 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-4800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-6300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>223700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>8100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-10100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>25900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>51500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>24700</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
@@ -2657,34 +2718,34 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>4500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>28200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>62500</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>52200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>46600</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-19200</v>
+        <v>500</v>
       </c>
       <c r="E32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F32" s="3">
         <v>1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>52400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-50100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-60900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E33" s="3">
         <v>3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-204900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>198900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>52100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>30000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-24200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>55600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>77800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>67300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>77500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>93200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>90000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>172800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>62800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>57200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>69200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>45500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E35" s="3">
         <v>3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-204900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>198900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>52100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>30000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-24200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>55600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>77800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>67300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>77500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>93200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>90000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>172800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>62800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>57200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>69200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>45500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E41" s="3">
         <v>93500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>110300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>242400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>219600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>225700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>148700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>804400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>134200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>177600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>631900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>621600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>759000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>752100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1276700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>968500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>293100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>507600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>508600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>233000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>265600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>277100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>455100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>369800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>330800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>317200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>432100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>530400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>188000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>201800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>323100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,103 +3718,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2683700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2573800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2698100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2712000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2725700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2665800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2953500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3085800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3168100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2887300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2733000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2634100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2618200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2256200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2216900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2108600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2173900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2557700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2605800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2648400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2937300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2455400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2817100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2785200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2883500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2625100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2558300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2435000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2521400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2463100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2457400</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,198 +3914,207 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>169400</v>
+      </c>
+      <c r="E45" s="3">
         <v>174600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>132400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>129700</v>
       </c>
       <c r="G45" s="3">
         <v>129700</v>
       </c>
       <c r="H45" s="3">
+        <v>129700</v>
+      </c>
+      <c r="I45" s="3">
         <v>130900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>106300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2202700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>326900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>163300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>158900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>148300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>166900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>181000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>174000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>245900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>179200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>143300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>167500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>257300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>581700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>199400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>206300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>196800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>195100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>183700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>170700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>178200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>176300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>153800</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2958300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2841900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2940800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3084100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3075000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3022400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3202900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3996500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5505000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3391800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3528200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3414600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3525500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3175200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3674600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3251100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2712900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3244500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3257700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3048900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3460200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3314200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3471600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3361300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3411100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3137400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3174100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3136100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2887600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2841200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2934300</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4103,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>236500</v>
+      </c>
+      <c r="E48" s="3">
         <v>245700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>192800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>198700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>203000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>208400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>217200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>228800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>235400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>238200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>901300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>918600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>921200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>940500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>940100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>936800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>952700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>973100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>969500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>965500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1770800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2463800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>912000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>904500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>909600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>908200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>870500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>841300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>837500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>842500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>827700</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1573600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1588800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1547800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1566100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1825300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1831700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1824700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1850400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1985400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2000400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2673700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2696600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2617800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2641700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2251200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2261100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2300400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2328100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2324200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2336500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3052100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2535200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2878900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2889400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2909200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2917900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2818400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2837800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2814200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2838100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2787600</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E52" s="3">
         <v>49900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>47900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>48500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>44600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>57300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>56500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>50300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>66600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1820300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>67000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>88500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>95700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>40800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>44000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>45000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>33700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>35500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>28300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>41000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1084300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>38100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>38900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>36300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>20800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>42600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>41500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>40900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>35800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4818400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4726300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4729300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4897400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5147900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5119800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5301300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6126000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7792400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7450700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7170200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7118300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7160200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6798200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6909900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6494000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5999700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6581200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6579700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6377800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8324100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7206200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7300600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7194100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7266200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6984300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6905600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6856700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6580200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6557600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6586400</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>744100</v>
+      </c>
+      <c r="E57" s="3">
         <v>556600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>646400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>625700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>683800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>551200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>645600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>736100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>833500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>785300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1070200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1074500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1118100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>688900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>938100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>983800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>354300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>704600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>718500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>847100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>997800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>691300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>870300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>874400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>942700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>682700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>754600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>735500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>786500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>648500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>700300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E58" s="3">
         <v>155500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>42300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>187900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>225800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>290600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>283600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>760900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1034000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>19100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>22700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>30400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>24300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>26400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>26900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>27000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>42100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>39000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>105500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>148200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>13100</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>17700</v>
       </c>
       <c r="Z58" s="3">
         <v>17700</v>
       </c>
       <c r="AA58" s="3">
+        <v>17700</v>
+      </c>
+      <c r="AB58" s="3">
         <v>16800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>12400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>16800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>17700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>38000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>105200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1709200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1766700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1820000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1832600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1756800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1801400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1891200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2050900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2614300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2374000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1667400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1586100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1507500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1537400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1390000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>998600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1637500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1771000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1758700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1715800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1799600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1920400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1736900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1672100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1668400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1694100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1576200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1509700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1509100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1581300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1558900</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2573700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2478800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2508700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2646200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2666400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2643200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2820400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3547900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4481800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3009300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2756700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2683300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2656000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2250600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2354500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2009300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2018800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2517700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2516200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2668400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2945600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2624800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2624900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2564200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2627900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2389200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2347600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2262900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2333600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2335000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2283900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200500</v>
+      </c>
+      <c r="E61" s="3">
         <v>202400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>201400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>201000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>206000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>206200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>194700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>190700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>939800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1852700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1850700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1851800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1852800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1853800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1854800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1856900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1860100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1875300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1877600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1403800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2676000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2654300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2657600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2660900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2664300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2667700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2671000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2675200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2360500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2365100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2371800</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E62" s="3">
         <v>105600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>101100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>103300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>137100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>139600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>139300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>146000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>253300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>484800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>499700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>511900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>504100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>528200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>553600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>545100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>549000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>538000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>550100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>553000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1200000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>462900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>456600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>456500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>453900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>442500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>484300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>456800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>455700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>460200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>452900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2875700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2786800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2811200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2950500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3009500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2989000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3154400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3884600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5674900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5346800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5107100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5047000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5012900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4632600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4762900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4411300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4427900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4931000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4943900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4625200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6821600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5742000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5739100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5681600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5746100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5499400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5502900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5394900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5149800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5160300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5108600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6040,32 +6208,32 @@
         <v>612500</v>
       </c>
       <c r="K70" s="3">
+        <v>612500</v>
+      </c>
+      <c r="L70" s="3">
         <v>601600</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>590900</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>580400</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>570000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>559800</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>549800</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>540000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>528200</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>631800</v>
+      </c>
+      <c r="E72" s="3">
         <v>624400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>621200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>619600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>824500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>822900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>796900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>813800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>614600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>625700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>631100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>642500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>641200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>600700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>627800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>592500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>624800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>651000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>655700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>644900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>422900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>392300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>371500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>341100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>295000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>257000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>131300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>111800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>98600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>74100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1330200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1327000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1305600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1334400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1525900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1518300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1534400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1628900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1515900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1513000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1482700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1501300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1587500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1615800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1607000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1554500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1571800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1650200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1635800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1752600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1502500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1464200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1561500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1512500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1520100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1484900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1402700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1430400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1397300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1477800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E81" s="3">
         <v>3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-204900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>198900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>52100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>30000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-24200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>55600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>77800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>67300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>77500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>93200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>90000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>172800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>62800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>57200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>69200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>45500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E83" s="3">
         <v>25300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>26800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>51900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>44700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>92400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>47000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>50600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>46500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>94200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>47700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>50100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>46400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>26100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>66100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>67100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>65600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>66900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>70300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>69400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>66200</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>64500</v>
       </c>
       <c r="AE83" s="3">
         <v>64500</v>
       </c>
       <c r="AF83" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AG83" s="3">
         <v>64700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100200</v>
+      </c>
+      <c r="E89" s="3">
         <v>19300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>73600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>46400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>96100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-125300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-326900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-86100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>73300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>59800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>295700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>164500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>163000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>268900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-49200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>94200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>130300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>223800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>93700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>164000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>199100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>234400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>152300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>100900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>114000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>231900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>142000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>87100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-46700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-29600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-34000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-49200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-46100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-32300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-48600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-31300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-34700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-74400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-73200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-161500</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-51300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>12400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-38000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>164400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>109800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1873200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-258500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-803600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-89300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-325700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-79200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-590200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-222300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>485900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>116700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-47700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-98400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-150300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-156000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-147100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-68600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-74000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-91500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-109600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-134400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-99800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8166,55 +8400,58 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-49000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-24500</v>
       </c>
       <c r="T96" s="3">
         <v>-24500</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-24500</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-93300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-46500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-47100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-47000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-47200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-43300</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-43900</v>
       </c>
       <c r="AD96" s="3">
         <v>-43900</v>
       </c>
       <c r="AE96" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-43700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-40100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-40000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-63600</v>
+      </c>
+      <c r="E100" s="3">
         <v>32200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-116500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-81900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-618100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-911100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>298700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>273100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>50600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-113300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-88700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>105900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>368800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-279900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-197200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-23300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>247100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-51700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-18300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-114400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-48200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-115700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-41800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-34500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-110900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>174200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-136400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-59300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-13900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E101" s="3">
         <v>6600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-21300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>6400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>12700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-17300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-23700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>8500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>6800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-120400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>100100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-654900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>629100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-42900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-455600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-136900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-519100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>312900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>457600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-153400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>29000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>275200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>26800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-74800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-113000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>87200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>39100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>14800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-115600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-98000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>342300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-121300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>8400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>KAR</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>431800</v>
+      </c>
+      <c r="E8" s="3">
         <v>416300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>391300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>416300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>416900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>420600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>372800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>393000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>753600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>369400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>357700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>347100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>745800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>369800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>529600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>593600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1064500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>645500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>671300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>701900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>719100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>689600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>593800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>612400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>956600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>950500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>890400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>843000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>858000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>866600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>859500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>789600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>245900</v>
+      </c>
+      <c r="E9" s="3">
         <v>213900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>204800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>216000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>222600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>224200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>202000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>209600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>422700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>210800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>194200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>185700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>412600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>203800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>325400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>329700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>629700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>394600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>394900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>410900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>417400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>393900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>332300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>330700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>531300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>535000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>525100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>479200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>481700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>501200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>534100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>459500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>185900</v>
+      </c>
+      <c r="E10" s="3">
         <v>202400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>186500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>194300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>196400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>170800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>183400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>330900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>158600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>163500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>161400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>333200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>166000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>204200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>263900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>434800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>250900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>276400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>291000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>301700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>295700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>261500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>281700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>425300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>415500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>365300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>363800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>376300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>365400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>325400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>330100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,76 +1338,79 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-700</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>233200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-44400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>11200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>29800</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2200</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1398,127 +1418,133 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>27500</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>1400</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E15" s="3">
         <v>24300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>25300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>26400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>23000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>51900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>26000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>28200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>27400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>54300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>26900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>50600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>46500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>94200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>47700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>50100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>46400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>47900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>44300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>42600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>41400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>66900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>70300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>69400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>66200</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>64500</v>
       </c>
       <c r="AF15" s="3">
         <v>64500</v>
       </c>
       <c r="AG15" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AH15" s="3">
         <v>64700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>376000</v>
+      </c>
+      <c r="E17" s="3">
         <v>346900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>333200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>349800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>593800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>366200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>285300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>352300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>725300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>355700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>280200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>322300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>696300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>349200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>515700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>507200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1028400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>604700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>609700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>618400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>628500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>613400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>523600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>526800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>781000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>792700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>767000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>701100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>728300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>723100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>749000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>666300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E18" s="3">
         <v>69400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>58100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>66500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-176900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>54400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>87500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>40700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>77500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>24800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>49500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>20600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>86400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>36100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>40800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>61600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>83500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>90600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>76200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>70200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>85600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>175600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>157800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>123400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>141900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>129700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>143500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>110500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>123300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-52400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>50100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>60900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>23000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E21" s="3">
         <v>93200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>85800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>91200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-147500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>81300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>119200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>63800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>75000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>38500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>53300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>42700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>153900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>108400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>60600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>134000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>131000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>90500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>114200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>131900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>139200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>122100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>111500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>130200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>196400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>232900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>215800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>208300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>195300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>208000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>174900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E22" s="3">
         <v>39700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>39300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>39400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>38800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>38300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>35400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>32300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>51500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>32000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>61800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>30800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>29500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>68900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>38000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>39500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>37900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>55200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>56000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>52000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>49200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>49900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>46200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>43300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>41600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>39700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>40200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>38000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>36300</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E23" s="3">
         <v>29200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>25400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-213100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>20000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>59800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>37800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>50700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>58000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-32100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>24600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>47600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>36100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>21800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>16900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>39600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>128400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>116400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>103100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>100500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>91100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>103300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>72200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>86200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E24" s="3">
         <v>10700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-19300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>17900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-14600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-22100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>26900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>13200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>8700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>35200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>26400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>37700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>33900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>34100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>26700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E26" s="3">
         <v>18500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-193800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>41900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>26200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>47100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-29500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>34400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>27400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>30900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>93200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>90000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>81200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>62800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>57200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>69200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>45500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
         <v>5600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-204900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>23800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-37300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>30000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-24200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>34400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>27400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>30900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>93200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>90000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>81200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>62800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>57200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>69200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>45500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,20 +2722,23 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>700</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
@@ -2685,32 +2746,32 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-4800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-6300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>223700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>8100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-10100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>25900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>51500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>24700</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
@@ -2721,34 +2782,34 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>4500</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>28200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>62500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>52200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>46600</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>52400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-50100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-23000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E33" s="3">
         <v>5600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-204900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>198900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>52100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>37600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>30000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-24200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>55600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>77800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>67300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>77500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>93200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>90000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>172800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>62800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>57200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>69200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>45500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E35" s="3">
         <v>5600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-204900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>198900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>52100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>37600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>30000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-24200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>55600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>77800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>67300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>77500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>93200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>90000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>172800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>62800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>57200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>69200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>45500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E41" s="3">
         <v>105200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>93500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>110300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>242400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>219600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>225700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>148700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>804400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>134200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>177600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>631900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>621600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>759000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>752100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1276700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>968500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>293100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>507600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>508600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>233000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>265600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>277100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>455100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>369800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>330800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>317200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>432100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>530400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>188000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>201800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>323100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2512200</v>
+      </c>
+      <c r="E43" s="3">
         <v>2683700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2573800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2698100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2712000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2725700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2665800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2953500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3085800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3168100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2887300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2733000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2634100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2618200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2256200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2216900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2108600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2173900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2557700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2605800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2648400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2937300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2455400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2817100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2785200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2883500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2625100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2558300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2435000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2521400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2463100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2457400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,204 +4013,213 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E45" s="3">
         <v>169400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>174600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>132400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>129700</v>
       </c>
       <c r="H45" s="3">
         <v>129700</v>
       </c>
       <c r="I45" s="3">
+        <v>129700</v>
+      </c>
+      <c r="J45" s="3">
         <v>130900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>106300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2202700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>326900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>163300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>158900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>148300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>166900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>181000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>174000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>245900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>179200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>143300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>167500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>257300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>581700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>199400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>206300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>196800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>195100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>183700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>170700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>178200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>176300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>153800</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2774100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2958300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2841900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2940800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3084100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3075000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3022400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3202900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3996500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5505000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3391800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3528200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3414600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3525500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3175200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3674600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3251100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2712900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3244500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3257700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3048900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3460200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3314200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3471600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3361300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3411100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3137400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3174100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3136100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2887600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2841200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2934300</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>231700</v>
+      </c>
+      <c r="E48" s="3">
         <v>236500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>245700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>192800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>198700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>203000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>208400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>217200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>228800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>235400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>238200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>901300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>918600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>921200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>940500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>940100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>936800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>952700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>973100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>969500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>965500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1770800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2463800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>912000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>904500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>909600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>908200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>870500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>841300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>837500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>842500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>827700</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1562100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1573600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1588800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1547800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1566100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1825300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1831700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1824700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1850400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1985400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2000400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2673700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2696600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2617800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2641700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2251200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2261100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2300400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2328100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2324200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2336500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3052100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2535200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2878900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2889400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2909200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2917900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2818400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2837800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2814200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2838100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2787600</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E52" s="3">
         <v>50000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>49900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>47900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>48500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>44600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>57300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>56500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>50300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>66600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1820300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>67000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>88500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>95700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>40800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>44000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>45000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>33700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>35500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>28300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>41000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1084300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>38100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>38900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>36300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>20800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>42600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>41500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>40900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>35800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4617800</v>
+      </c>
+      <c r="E54" s="3">
         <v>4818400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4726300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4729300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4897400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5147900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5119800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5301300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6126000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7792400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7450700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7170200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7118300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7160200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6798200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6909900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6494000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5999700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6581200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6579700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6377800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8324100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7206200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7300600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7194100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7266200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6984300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6905600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6856700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6580200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6557600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6586400</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600300</v>
+      </c>
+      <c r="E57" s="3">
         <v>744100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>556600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>646400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>625700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>683800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>551200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>645600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>736100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>833500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>785300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1070200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1074500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1118100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>688900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>938100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>983800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>354300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>704600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>718500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>847100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>997800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>691300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>870300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>874400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>942700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>682700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>754600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>735500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>786500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>648500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>700300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>272000</v>
+      </c>
+      <c r="E58" s="3">
         <v>120400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>155500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>42300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>187900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>225800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>290600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>283600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>760900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1034000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>19900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>22700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>30400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>24300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>26400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>26900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>42100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>39000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>105500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>148200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>13100</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>17700</v>
       </c>
       <c r="AA58" s="3">
         <v>17700</v>
       </c>
       <c r="AB58" s="3">
+        <v>17700</v>
+      </c>
+      <c r="AC58" s="3">
         <v>16800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>12400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>16800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>38000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>105200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1703800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1709200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1766700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1820000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1832600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1756800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1801400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1891200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2050900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2614300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2374000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1667400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1586100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1507500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1537400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1390000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>998600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1637500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1771000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1758700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1715800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1799600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1920400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1736900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1672100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1668400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1694100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1576200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1509700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1509100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1581300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1558900</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2576100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2573700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2478800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2508700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2646200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2666400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2643200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2820400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3547900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4481800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3009300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2756700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2683300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2656000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2250600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2354500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2009300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2018800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2517700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2516200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2668400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2945600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2624800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2624900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2564200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2627900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2389200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2347600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2262900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2333600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2335000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2283900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>200500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>202400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>201400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>201000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>206000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>206200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>194700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>190700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>939800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1852700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1850700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1851800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1852800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1853800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1854800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1856900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1860100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1875300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1877600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1403800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2676000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2654300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2657600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2660900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2664300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2667700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2671000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2675200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2360500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2365100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2371800</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E62" s="3">
         <v>101500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>105600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>101100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>103300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>137100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>139600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>139300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>146000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>253300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>484800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>499700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>511900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>504100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>528200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>553600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>545100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>549000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>538000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>550100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>553000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1200000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>462900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>456600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>456500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>453900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>442500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>484300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>456800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>455700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>460200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>452900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2677100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2875700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2786800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2811200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2950500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3009500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2989000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3154400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3884600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5674900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5346800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5107100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5047000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5012900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4632600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4762900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4411300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4427900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4931000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4943900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4625200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6821600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5742000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5739100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5681600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5746100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5499400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5502900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5394900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5149800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5160300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5108600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6211,32 +6379,32 @@
         <v>612500</v>
       </c>
       <c r="L70" s="3">
+        <v>612500</v>
+      </c>
+      <c r="M70" s="3">
         <v>601600</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>590900</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>580400</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>570000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>559800</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>549800</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>540000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>528200</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>631300</v>
+      </c>
+      <c r="E72" s="3">
         <v>631800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>624400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>621200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>619600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>824500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>822900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>796900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>813800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>614600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>625700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>631100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>642500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>641200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>600700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>627800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>592500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>624800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>651000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>655700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>644900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>422900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>392300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>371500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>341100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>295000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>257000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>131300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>111800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>98600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>74100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1328200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1330200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1327000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1305600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1334400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1525900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1518300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1534400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1628900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1515900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1513000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1482700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1501300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1587500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1615800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1607000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1554500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1571800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1650200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1635800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1752600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1502500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1464200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1561500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1512500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1520100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1484900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1402700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1430400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1397300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1477800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E81" s="3">
         <v>5600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-204900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>198900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>52100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>37600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>30000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-24200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>55600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>77800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>67300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>77500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>93200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>90000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>172800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>62800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>57200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>69200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>45500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E83" s="3">
         <v>24300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>26400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>26800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>51900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>44700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>92400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>47000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>50600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>46500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>94200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>47700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>50100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>46400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>26100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>66100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>67100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>65600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>66900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>70300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>69400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>66200</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>64500</v>
       </c>
       <c r="AF83" s="3">
         <v>64500</v>
       </c>
       <c r="AG83" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AH83" s="3">
         <v>64700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E89" s="3">
         <v>100200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>73600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>46400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>96100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-125300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-326900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-86100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>73300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>59800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>295700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>164500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-47500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>163000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>268900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-49200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>94200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>130300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>223800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>93700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>164000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>199100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>234400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>152300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>100900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>114000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>231900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>142000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>87100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-18000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-46700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-29600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-34000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-49200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-46100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-32300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-48600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-31300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-34700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-74400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-73200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-161500</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-39700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-51300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>12400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-38000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>164400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>109800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1873200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-258500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-803600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-89300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-325700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-79200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-590200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-222300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>485900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>116700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-47700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-98400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-150300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-156000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-147100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-68600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-74000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-91500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-109600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-134400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-99800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8403,55 +8637,58 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-49000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-24500</v>
       </c>
       <c r="U96" s="3">
         <v>-24500</v>
       </c>
       <c r="V96" s="3">
-        <v>0</v>
+        <v>-24500</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-93300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-46500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-47100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-47200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-43300</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-43900</v>
       </c>
       <c r="AE96" s="3">
         <v>-43900</v>
       </c>
       <c r="AF96" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-43700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-40100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-40000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-102900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-63600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>32200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-116500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-81900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-618100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-911100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>298700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>273100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>50600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-113300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-88700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>105900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>368800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-279900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-197200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-23300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>247100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-51700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-18300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-114400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-48200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-115700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-41800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-34500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-110900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>174200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-136400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-59300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-13900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-21300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>6400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>12700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-17300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-23700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-120400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-654900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>629100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-42900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-455600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-136900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-519100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>312900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>457600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-153400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>29000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>275200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>26800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-74800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-113000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>87200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>39100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-115600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-98000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>342300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-121300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>8400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>KAR</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>448400</v>
+      </c>
+      <c r="E8" s="3">
         <v>431800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>416300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>391300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>416300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>416900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>420600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>372800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>393000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>753600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>369400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>357700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>347100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>745800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>369800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>529600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>593600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1064500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>645500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>671300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>701900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>719100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>689600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>593800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>612400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>956600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>950500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>890400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>843000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>858000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>866600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>859500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>789600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>252000</v>
+      </c>
+      <c r="E9" s="3">
         <v>245900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>213900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>204800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>216000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>222600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>224200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>202000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>209600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>422700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>210800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>194200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>185700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>412600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>203800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>325400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>329700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>629700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>394600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>394900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>410900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>417400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>393900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>332300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>330700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>531300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>535000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>525100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>479200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>481700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>501200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>534100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>459500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>196400</v>
+      </c>
+      <c r="E10" s="3">
         <v>185900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>202400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>186500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>200300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>194300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>196400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>170800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>183400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>330900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>158600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>163500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>161400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>333200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>166000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>204200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>263900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>434800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>250900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>276400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>291000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>301700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>295700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>261500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>281700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>425300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>415500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>365300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>363800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>376300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>365400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>325400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>330100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,79 +1358,82 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>-700</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="H14" s="3">
-        <v>233200</v>
+        <v>500</v>
       </c>
       <c r="I14" s="3">
-        <v>11000</v>
+        <v>233000</v>
       </c>
       <c r="J14" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-44400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>15700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>29800</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>2200</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1421,130 +1441,136 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>27500</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>1400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E15" s="3">
         <v>24100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>25300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>23000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>51900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>26000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>28200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>27400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>54300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>26900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>50600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>46500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>94200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>47700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>50100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>46400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>47900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>44300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>42600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>41400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>66900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>70300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>69400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>66200</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>64500</v>
       </c>
       <c r="AG15" s="3">
         <v>64500</v>
       </c>
       <c r="AH15" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AI15" s="3">
         <v>64700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>375200</v>
+      </c>
+      <c r="E17" s="3">
         <v>376000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>346900</v>
       </c>
-      <c r="F17" s="3">
-        <v>333200</v>
-      </c>
       <c r="G17" s="3">
+        <v>333900</v>
+      </c>
+      <c r="H17" s="3">
         <v>349800</v>
       </c>
-      <c r="H17" s="3">
-        <v>593800</v>
-      </c>
       <c r="I17" s="3">
-        <v>366200</v>
+        <v>360600</v>
       </c>
       <c r="J17" s="3">
+        <v>355200</v>
+      </c>
+      <c r="K17" s="3">
         <v>285300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>352300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>725300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>355700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>280200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>322300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>696300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>349200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>515700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>507200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1028400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>604700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>609700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>618400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>628500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>613400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>523600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>526800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>781000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>792700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>767000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>701100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>728300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>723100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>749000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>666300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E18" s="3">
         <v>55800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>69400</v>
       </c>
-      <c r="F18" s="3">
-        <v>58100</v>
-      </c>
       <c r="G18" s="3">
+        <v>57400</v>
+      </c>
+      <c r="H18" s="3">
         <v>66500</v>
       </c>
-      <c r="H18" s="3">
-        <v>-176900</v>
-      </c>
       <c r="I18" s="3">
-        <v>54400</v>
+        <v>56300</v>
       </c>
       <c r="J18" s="3">
+        <v>65400</v>
+      </c>
+      <c r="K18" s="3">
         <v>87500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>40700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>77500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>24800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>49500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>86400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>36100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>40800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>61600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>83500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>90600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>76200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>70200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>85600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>175600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>157800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>123400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>141900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>129700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>143500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>110500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>123300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-200</v>
+        <v>-3600</v>
       </c>
       <c r="E20" s="3">
-        <v>-500</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>2400</v>
+        <v>500</v>
       </c>
       <c r="G20" s="3">
-        <v>-1700</v>
+        <v>-2700</v>
       </c>
       <c r="H20" s="3">
-        <v>2600</v>
+        <v>1200</v>
       </c>
       <c r="I20" s="3">
-        <v>3900</v>
+        <v>-2400</v>
       </c>
       <c r="J20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K20" s="3">
         <v>7700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-52400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>50100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>60900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>23000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1100</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E21" s="3">
         <v>79700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>93200</v>
       </c>
-      <c r="F21" s="3">
-        <v>85800</v>
-      </c>
       <c r="G21" s="3">
-        <v>91200</v>
+        <v>85400</v>
       </c>
       <c r="H21" s="3">
-        <v>-147500</v>
+        <v>91700</v>
       </c>
       <c r="I21" s="3">
-        <v>81300</v>
+        <v>85500</v>
       </c>
       <c r="J21" s="3">
+        <v>92400</v>
+      </c>
+      <c r="K21" s="3">
         <v>119200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>63800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>75000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>53300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>42700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>153900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>108400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>60600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>134000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>131000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>90500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>114200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>131900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>139200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>122100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>111500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>130200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>196400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>232900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>215800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>208300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>195300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>208000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>174900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E22" s="3">
         <v>37400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>39700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>39300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>39400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>38800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>32300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>51500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>32000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>31900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>61800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>30500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>29500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>68900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>38000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>39500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>37900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>55200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>56000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>52000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>49200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>49900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>46200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>43300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>41600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>39700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>40200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>38000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>36300</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E23" s="3">
         <v>18200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>29200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>25400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-213100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>59800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>37800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>50700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>58000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-32100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>47600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>21800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>16900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>39600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>128400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>116400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>103100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>100500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>91100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>103300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>72200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>86200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E24" s="3">
         <v>7500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-19300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-14600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-22100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>26900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>13200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>8700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>35200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>26400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>21900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>37700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>33900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>34100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>26700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E26" s="3">
         <v>10700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-193800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>41900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>26200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>47100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-29500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>34400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>27400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>30900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>93200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>90000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>81200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>62800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>57200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>69200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>45500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5600</v>
       </c>
-      <c r="F27" s="3">
-        <v>2500</v>
-      </c>
       <c r="G27" s="3">
+        <v>14300</v>
+      </c>
+      <c r="H27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-204900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>23800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-37300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>12900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-24200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>34400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>27400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>15100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>30900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>93200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>90000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>81200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>62800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>57200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>69200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>45500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,23 +2783,26 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>700</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -2749,32 +2810,32 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-4800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-6300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>223700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>8100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-10100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>25900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>51500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>24700</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -2785,34 +2846,34 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>4500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>28200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>62500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>52200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>46600</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>200</v>
+        <v>3600</v>
       </c>
       <c r="E32" s="3">
-        <v>500</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>-2400</v>
+        <v>-500</v>
       </c>
       <c r="G32" s="3">
-        <v>1700</v>
+        <v>2700</v>
       </c>
       <c r="H32" s="3">
-        <v>-2600</v>
+        <v>-1200</v>
       </c>
       <c r="I32" s="3">
-        <v>-3900</v>
+        <v>2400</v>
       </c>
       <c r="J32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-7700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>52400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-50100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-60900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-400</v>
+        <v>28400</v>
       </c>
       <c r="E33" s="3">
-        <v>5600</v>
+        <v>10700</v>
       </c>
       <c r="F33" s="3">
-        <v>3200</v>
+        <v>18500</v>
       </c>
       <c r="G33" s="3">
-        <v>1200</v>
+        <v>14300</v>
       </c>
       <c r="H33" s="3">
-        <v>-204900</v>
+        <v>12700</v>
       </c>
       <c r="I33" s="3">
-        <v>1200</v>
+        <v>-193800</v>
       </c>
       <c r="J33" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K33" s="3">
         <v>19000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>198900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>52100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>37600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>30000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-24200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>35300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>55600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>77800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>67300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>77500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>93200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>90000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>172800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>62800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>57200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>69200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>45500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-400</v>
+        <v>28400</v>
       </c>
       <c r="E35" s="3">
-        <v>5600</v>
+        <v>10700</v>
       </c>
       <c r="F35" s="3">
-        <v>3200</v>
+        <v>18500</v>
       </c>
       <c r="G35" s="3">
-        <v>1200</v>
+        <v>14300</v>
       </c>
       <c r="H35" s="3">
-        <v>-204900</v>
+        <v>12700</v>
       </c>
       <c r="I35" s="3">
-        <v>1200</v>
+        <v>-193800</v>
       </c>
       <c r="J35" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K35" s="3">
         <v>19000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>198900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>52100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>37600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>30000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-24200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>35300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>55600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>77800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>67300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>77500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>93200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>90000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>172800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>62800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>57200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>69200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>45500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E41" s="3">
         <v>60900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>105200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>93500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>242400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>219600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>225700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>148700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>804400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>134200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>177600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>631900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>621600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>759000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>752100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1276700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>968500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>293100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>507600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>508600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>233000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>265600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>277100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>455100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>369800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>330800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>317200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>432100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>530400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>188000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>201800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>323100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,132 +3904,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2492500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2512200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2683700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2573800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2698100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2712000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2725700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2665800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2953500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3085800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3168100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2887300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2733000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2634100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2618200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2256200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2216900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2108600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2173900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2557700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2605800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2648400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2937300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2455400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2817100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2785200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2883500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2625100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2558300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2435000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2521400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2463100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2457400</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,233 +4112,242 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>201000</v>
+        <v>131700</v>
       </c>
       <c r="E45" s="3">
-        <v>169400</v>
+        <v>133300</v>
       </c>
       <c r="F45" s="3">
-        <v>174600</v>
+        <v>123700</v>
       </c>
       <c r="G45" s="3">
-        <v>132400</v>
+        <v>109200</v>
       </c>
       <c r="H45" s="3">
-        <v>129700</v>
+        <v>90600</v>
       </c>
       <c r="I45" s="3">
-        <v>129700</v>
+        <v>99600</v>
       </c>
       <c r="J45" s="3">
+        <v>97500</v>
+      </c>
+      <c r="K45" s="3">
         <v>130900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>106300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2202700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>326900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>163300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>158900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>148300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>166900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>181000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>174000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>245900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>179200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>143300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>167500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>257300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>581700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>199400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>206300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>196800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>195100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>183700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>170700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>178200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>176300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>153800</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2784800</v>
+      </c>
+      <c r="E46" s="3">
         <v>2774100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2958300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2841900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2940800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3084100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3075000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3022400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3202900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3996500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5505000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3391800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3528200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3414600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3525500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3175200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3674600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3251100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2712900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3244500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3257700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3048900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3460200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3314200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3471600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3361300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3411100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3137400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3174100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3136100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2887600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2841200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2934300</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
+        <v>25700</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>24900</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,210 +4424,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>230200</v>
+      </c>
+      <c r="E48" s="3">
         <v>231700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>236500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>245700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>192800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>198700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>203000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>208400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>217200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>228800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>235400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>238200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>901300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>918600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>921200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>940500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>940100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>936800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>952700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>973100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>969500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>965500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1770800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2463800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>912000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>904500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>909600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>908200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>870500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>841300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>837500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>842500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>827700</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1559500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1562100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1573600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1588800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1547800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1566100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1825300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1831700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1824700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1850400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1985400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2000400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2673700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2696600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2617800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2641700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2251200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2261100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2300400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2328100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2324200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2336500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3052100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2535200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2878900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2889400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2909200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2917900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2818400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2837800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2814200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2838100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2787600</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E52" s="3">
         <v>49900</v>
       </c>
-      <c r="E52" s="3">
-        <v>50000</v>
-      </c>
       <c r="F52" s="3">
-        <v>49900</v>
+        <v>23600</v>
       </c>
       <c r="G52" s="3">
-        <v>47900</v>
+        <v>23900</v>
       </c>
       <c r="H52" s="3">
+        <v>22200</v>
+      </c>
+      <c r="I52" s="3">
         <v>48500</v>
       </c>
-      <c r="I52" s="3">
-        <v>44600</v>
-      </c>
       <c r="J52" s="3">
+        <v>19700</v>
+      </c>
+      <c r="K52" s="3">
         <v>57300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>56500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>50300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>66600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1820300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>67000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>88500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>95700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>40800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>44000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>45000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>33700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>35500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>28300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>26900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>41000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1084300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>38100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>38900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>36300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>42600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>41500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>40900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>35800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4625800</v>
+      </c>
+      <c r="E54" s="3">
         <v>4617800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4818400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4726300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4729300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4897400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5147900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5119800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5301300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6126000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7792400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7450700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7170200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7118300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7160200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6798200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6909900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6494000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5999700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6581200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6579700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6377800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8324100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7206200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7300600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7194100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7266200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6984300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6905600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6856700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6580200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6557600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6586400</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>650800</v>
+      </c>
+      <c r="E57" s="3">
         <v>600300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>744100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>556600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>646400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>625700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>683800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>551200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>645600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>736100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>833500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>785300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1070200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1074500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1118100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>688900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>938100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>983800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>354300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>704600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>718500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>847100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>997800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>691300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>870300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>874400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>942700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>682700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>754600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>735500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>786500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>648500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>700300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>272000</v>
+        <v>1796600</v>
       </c>
       <c r="E58" s="3">
-        <v>120400</v>
+        <v>1845600</v>
       </c>
       <c r="F58" s="3">
-        <v>155500</v>
+        <v>1717600</v>
       </c>
       <c r="G58" s="3">
-        <v>42300</v>
+        <v>1798400</v>
       </c>
       <c r="H58" s="3">
-        <v>187900</v>
+        <v>1737600</v>
       </c>
       <c r="I58" s="3">
-        <v>225800</v>
+        <v>1905300</v>
       </c>
       <c r="J58" s="3">
+        <v>1864000</v>
+      </c>
+      <c r="K58" s="3">
         <v>290600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>283600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>760900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1034000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>19100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>22700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>30400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>24300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>26400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>26900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>27000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>42100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>39000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>105500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>148200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>13100</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>17700</v>
       </c>
       <c r="AB58" s="3">
         <v>17700</v>
       </c>
       <c r="AC58" s="3">
+        <v>17700</v>
+      </c>
+      <c r="AD58" s="3">
         <v>16800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>12400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>16800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>38000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>105200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1703800</v>
+        <v>4400</v>
       </c>
       <c r="E59" s="3">
-        <v>1709200</v>
+        <v>3200</v>
       </c>
       <c r="F59" s="3">
-        <v>1766700</v>
+        <v>5000</v>
       </c>
       <c r="G59" s="3">
-        <v>1820000</v>
+        <v>9800</v>
       </c>
       <c r="H59" s="3">
-        <v>1832600</v>
+        <v>3300</v>
       </c>
       <c r="I59" s="3">
-        <v>1756800</v>
+        <v>2300</v>
       </c>
       <c r="J59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K59" s="3">
         <v>1801400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1891200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2050900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2614300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2374000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1667400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1586100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1507500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1537400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1390000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>998600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1637500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1771000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1758700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1715800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1799600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1920400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1736900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1672100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1668400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1694100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1576200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1509700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1509100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1581300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1558900</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2585300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2576100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2573700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2478800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2508700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2646200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2666400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2643200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2820400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3547900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4481800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3009300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2756700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2683300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2656000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2250600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2354500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2009300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2018800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2517700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2516200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2668400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2945600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2624800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2624900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2564200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2627900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2389200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2347600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2262900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2333600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2335000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2283900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>64100</v>
       </c>
       <c r="E61" s="3">
-        <v>200500</v>
+        <v>65500</v>
       </c>
       <c r="F61" s="3">
-        <v>202400</v>
+        <v>267900</v>
       </c>
       <c r="G61" s="3">
-        <v>201400</v>
+        <v>272800</v>
       </c>
       <c r="H61" s="3">
-        <v>201000</v>
+        <v>273800</v>
       </c>
       <c r="I61" s="3">
-        <v>206000</v>
+        <v>275900</v>
       </c>
       <c r="J61" s="3">
+        <v>283500</v>
+      </c>
+      <c r="K61" s="3">
         <v>206200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>194700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>190700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>939800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1852700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1850700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1851800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1852800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1853800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1854800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1856900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1860100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1875300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1877600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1403800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2676000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2654300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2657600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2660900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2664300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2667700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2671000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2675200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2360500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2365100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2371800</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>101000</v>
+        <v>15700</v>
       </c>
       <c r="E62" s="3">
-        <v>101500</v>
+        <v>15300</v>
       </c>
       <c r="F62" s="3">
-        <v>105600</v>
+        <v>14800</v>
       </c>
       <c r="G62" s="3">
-        <v>101100</v>
+        <v>14300</v>
       </c>
       <c r="H62" s="3">
-        <v>103300</v>
+        <v>5900</v>
       </c>
       <c r="I62" s="3">
-        <v>137100</v>
+        <v>6400</v>
       </c>
       <c r="J62" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K62" s="3">
         <v>139600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>139300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>146000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>253300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>484800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>499700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>511900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>504100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>528200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>553600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>545100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>549000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>538000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>550100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>553000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1200000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>462900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>456600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>456500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>453900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>442500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>484300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>456800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>455700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>460200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>452900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2686200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2677100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2875700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2786800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2811200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2950500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3009500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2989000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3154400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3884600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5674900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5346800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5107100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5047000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5012900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4632600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4762900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4411300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4427900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4931000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4943900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4625200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6821600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5742000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5739100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5681600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5746100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5499400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5502900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5394900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5149800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5160300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5108600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6382,32 +6550,32 @@
         <v>612500</v>
       </c>
       <c r="M70" s="3">
+        <v>612500</v>
+      </c>
+      <c r="N70" s="3">
         <v>601600</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>590900</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>580400</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>570000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>559800</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>549800</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>540000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>528200</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>648600</v>
+      </c>
+      <c r="E72" s="3">
         <v>631300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>631800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>624400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>621200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>619600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>824500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>822900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>796900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>813800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>614600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>625700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>631100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>642500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>641200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>600700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>627800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>592500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>624800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>651000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>655700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>644900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>422900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>392300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>371500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>341100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>295000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>257000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>131300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>111800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>98600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>74100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1327100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1328200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1330200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1327000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1305600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1334400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1525900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1518300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1534400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1628900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1515900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1513000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1482700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1501300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1587500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1615800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1607000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1554500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1571800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1650200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1635800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1752600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1502500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1464200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1561500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1512500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1520100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1484900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1402700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1430400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1397300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1477800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-400</v>
+        <v>28400</v>
       </c>
       <c r="E81" s="3">
-        <v>5600</v>
+        <v>10700</v>
       </c>
       <c r="F81" s="3">
-        <v>3200</v>
+        <v>18500</v>
       </c>
       <c r="G81" s="3">
-        <v>1200</v>
+        <v>14300</v>
       </c>
       <c r="H81" s="3">
-        <v>-204900</v>
+        <v>12700</v>
       </c>
       <c r="I81" s="3">
-        <v>1200</v>
+        <v>-193800</v>
       </c>
       <c r="J81" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K81" s="3">
         <v>19000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>198900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>52100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>37600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>30000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-24200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>35300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>55600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>77800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>67300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>77500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>93200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>90000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>172800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>62800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>57200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>69200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>45500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>24100</v>
-      </c>
-      <c r="E83" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="G83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="H83" s="3">
         <v>24300</v>
       </c>
-      <c r="F83" s="3">
-        <v>25300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>26400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>26800</v>
-      </c>
       <c r="I83" s="3">
-        <v>23000</v>
+        <v>25900</v>
       </c>
       <c r="J83" s="3">
+        <v>26000</v>
+      </c>
+      <c r="K83" s="3">
         <v>24000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>51900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>44700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>92400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>47000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>50600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>46500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>94200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>47700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>50100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>46400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>26100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>66100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>67100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>65600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>66900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>70300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>69400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>66200</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>64500</v>
       </c>
       <c r="AG83" s="3">
         <v>64500</v>
       </c>
       <c r="AH83" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AI83" s="3">
         <v>64700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>37400</v>
-      </c>
-      <c r="E89" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>100200</v>
       </c>
-      <c r="F89" s="3">
-        <v>19300</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>73600</v>
       </c>
-      <c r="H89" s="3">
-        <v>46400</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
         <v>96100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-125300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-326900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-86100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>73300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>59800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>295700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>164500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-47500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>163000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>268900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-49200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>94200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>130300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>223800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>93700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>164000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>199100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>234400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>152300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>100900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>114000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>231900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>142000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>87100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="E91" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-12900</v>
       </c>
-      <c r="F91" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>-12900</v>
       </c>
-      <c r="H91" s="3">
-        <v>-14900</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-12000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-46700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-29600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-34000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-49200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-46100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-32300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-48600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-31300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-34700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-74400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-73200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-161500</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>45600</v>
-      </c>
-      <c r="E94" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-39700</v>
       </c>
-      <c r="F94" s="3">
-        <v>-51300</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3">
         <v>12400</v>
       </c>
-      <c r="H94" s="3">
-        <v>-38000</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-6600</v>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J94" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="K94" s="3">
         <v>164400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>109800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1873200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-258500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-803600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-89300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-325700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-79200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-590200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-222300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>485900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>116700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-47700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-98400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-150300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-156000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-147100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-68600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-74000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-91500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-109600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-134400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-99800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8640,55 +8874,58 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-49000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-24500</v>
       </c>
       <c r="V96" s="3">
         <v>-24500</v>
       </c>
       <c r="W96" s="3">
-        <v>0</v>
+        <v>-24500</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-93300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-46500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-47100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-47200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-43300</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-43900</v>
       </c>
       <c r="AF96" s="3">
         <v>-43900</v>
       </c>
       <c r="AG96" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-43700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-40100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-40000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-102900</v>
-      </c>
-      <c r="E100" s="3">
+        <v>-97800</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>-63600</v>
       </c>
-      <c r="F100" s="3">
-        <v>32200</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>-200200</v>
       </c>
-      <c r="H100" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
         <v>-116500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-81900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-618100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-911100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>298700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>273100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>50600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-113300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-88700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>105900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>368800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-279900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-197200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-23300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>247100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-51700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-48200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-115700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-41800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-34500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-110900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>174200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-136400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-59300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-13900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-4900</v>
+        <v>-6200</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F101" s="3">
-        <v>6600</v>
+        <v>1100</v>
       </c>
       <c r="G101" s="3">
-        <v>-6200</v>
+        <v>8000</v>
       </c>
       <c r="H101" s="3">
-        <v>7700</v>
+        <v>-21300</v>
       </c>
       <c r="I101" s="3">
-        <v>1100</v>
+        <v>-9100</v>
       </c>
       <c r="J101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K101" s="3">
         <v>8000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-21300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-6100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>12700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-17300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-23700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>8500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>6200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-22300</v>
+        <v>32000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-8000</v>
       </c>
-      <c r="F102" s="3">
-        <v>6800</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-120400</v>
       </c>
-      <c r="H102" s="3">
-        <v>20700</v>
-      </c>
       <c r="I102" s="3">
-        <v>-25900</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="K102" s="3">
         <v>100100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-654900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>629100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-42900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-455600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-136900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-519100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>312900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>457600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-153400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>29000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>275200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>26800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-74800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-113000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>87200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>39100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>14800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-115600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-98000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>342300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-121300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>8400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>KAR</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E8" s="3">
         <v>448400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>431800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>416300</v>
       </c>
-      <c r="G8" s="3">
-        <v>391300</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>416300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>416900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>420600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>372800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>393000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>753600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>369400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>357700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>347100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>745800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>369800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>529600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>593600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1064500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>645500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>671300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>701900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>719100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>689600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>593800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>612400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>956600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>950500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>890400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>843000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>858000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>866600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>859500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>789600</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>244500</v>
+      </c>
+      <c r="E9" s="3">
         <v>252000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>245900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>213900</v>
       </c>
-      <c r="G9" s="3">
-        <v>204800</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
         <v>216000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>222600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>224200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>202000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>209600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>422700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>210800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>194200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>185700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>412600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>203800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>325400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>329700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>629700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>394600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>394900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>410900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>417400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>393900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>332300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>330700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>531300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>535000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>525100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>479200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>481700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>501200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>534100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>459500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>247500</v>
+      </c>
+      <c r="E10" s="3">
         <v>196400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>185900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>202400</v>
       </c>
-      <c r="G10" s="3">
-        <v>186500</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>200300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>194300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>196400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>170800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>183400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>330900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>158600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>163500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>161400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>333200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>166000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>204200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>263900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>434800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>250900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>276400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>291000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>301700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>295700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>261500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>281700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>425300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>415500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>365300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>363800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>376300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>365400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>325400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>330100</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,13 +1377,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-20400</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1375,68 +1394,68 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>233000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-44400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>15700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>29800</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2200</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1444,133 +1463,139 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>27500</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E15" s="3">
         <v>23800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>25300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>26800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>23000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>24300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>51900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>26000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>28200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>27400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>54300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>26900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>50600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>46500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>94200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>47700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>50100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>46400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>47900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>44300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>42600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>41400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>66900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>70300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>69400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>66200</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>64500</v>
       </c>
       <c r="AH15" s="3">
         <v>64500</v>
       </c>
       <c r="AI15" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>64700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>404700</v>
+      </c>
+      <c r="E17" s="3">
         <v>375200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>376000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>346900</v>
       </c>
-      <c r="G17" s="3">
-        <v>333900</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3">
         <v>349800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>360600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>355200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>285300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>352300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>725300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>355700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>280200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>322300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>696300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>349200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>515700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>507200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1028400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>604700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>609700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>618400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>628500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>613400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>523600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>526800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>781000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>792700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>767000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>701100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>728300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>723100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>749000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>666300</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E18" s="3">
         <v>73200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>55800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>69400</v>
       </c>
-      <c r="G18" s="3">
-        <v>57400</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
         <v>66500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>56300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>65400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>87500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>40700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>28300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>77500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>24800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>49500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>20600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>86400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>36100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>40800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>61600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>83500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>90600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>76200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>70200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>85600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>175600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>157800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>123400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>141900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>129700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>143500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>110500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>123300</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>129300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-52400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>50100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>60900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>23000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1100</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E21" s="3">
         <v>100600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>79700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>93200</v>
       </c>
-      <c r="G21" s="3">
-        <v>85400</v>
-      </c>
       <c r="H21" s="3">
+        <v>25300</v>
+      </c>
+      <c r="I21" s="3">
         <v>91700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>85500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>92400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>119200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>63800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>75000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>53300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>153900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>108400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>60600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>134000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>131000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>90500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>114200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>131900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>139200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>122100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>111500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>130200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>196400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>232900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>215800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>208300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>195300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>208000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>174900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-90600</v>
+      </c>
+      <c r="E22" s="3">
         <v>35300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>37400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>39700</v>
       </c>
-      <c r="G22" s="3">
-        <v>39300</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>39400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>38300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>35400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>32300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>32000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>31900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>61800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>30800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>30500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>29500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>68900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>38000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>39500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>37900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>55200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>56000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>52000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>49200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>49900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>43300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>41600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>39700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>40200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>38000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>36300</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E23" s="3">
         <v>41500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29200</v>
       </c>
-      <c r="G23" s="3">
-        <v>21200</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3">
         <v>25400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-213100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>59800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>37800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>50700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-20500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>58000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-32100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>47600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>36100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>21800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>16900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>39600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>128400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>116400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>103100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>100500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>91100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>103300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>72200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>86200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E24" s="3">
         <v>13100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10700</v>
       </c>
-      <c r="G24" s="3">
-        <v>7600</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3">
         <v>12700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-19300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-14600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-22100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>26900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>24500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>8700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>35200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>26400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>21900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>37700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>33900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>34100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>26700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E26" s="3">
         <v>28400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18500</v>
       </c>
-      <c r="G26" s="3">
-        <v>13600</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3">
         <v>12700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-193800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>41900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>26200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>47100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-29500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>15300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>34400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>27400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>30900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>93200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>90000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>81200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>62800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>57200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>69200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>45500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E27" s="3">
         <v>13000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5600</v>
       </c>
-      <c r="G27" s="3">
-        <v>14300</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-204900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-37300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>12900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-26900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>30000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-24200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>34400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>27400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>15300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>30900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>93200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>90000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>81200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>62800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>57200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>69200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>45500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2801,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -2813,32 +2873,32 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-4800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-6300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>223700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>8100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-10100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>25900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>51500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>24700</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
@@ -2849,35 +2909,35 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>4500</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>900</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>28200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>62500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>52200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>46600</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>91600</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-129300</v>
+      </c>
+      <c r="E32" s="3">
         <v>3600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>52400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-50100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-60900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E33" s="3">
         <v>28400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18500</v>
       </c>
-      <c r="G33" s="3">
-        <v>14300</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3">
         <v>12700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-193800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>198900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>52100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-26900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>30000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-24200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>55600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>77800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>67300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>77500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>93200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>90000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>172800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>62800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>57200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>69200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>45500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E35" s="3">
         <v>28400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18500</v>
       </c>
-      <c r="G35" s="3">
-        <v>14300</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3">
         <v>12700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-193800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>198900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>52100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-26900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>30000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-24200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>55600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>77800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>67300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>77500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>93200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>90000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>172800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>62800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>57200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>69200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>45500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E41" s="3">
         <v>132100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>60900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>105200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>93500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>110300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>242400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>219600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>225700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>148700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>804400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>134200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>177600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>631900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>621600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>759000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>752100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1276700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>968500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>293100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>507600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>508600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>233000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>265600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>277100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>455100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>369800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>330800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>317200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>432100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>530400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>188000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>201800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>323100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,112 +3996,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2570900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2492500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2512200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2683700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2573800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2698100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2712000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2725700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2665800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2953500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3085800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3168100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2887300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2733000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2634100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2618200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2256200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2216900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2108600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2173900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2557700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2605800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2648400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2937300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2455400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2817100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2785200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2883500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2625100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2558300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2435000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2521400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2463100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2457400</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,243 +4210,252 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>96900</v>
+      </c>
+      <c r="E45" s="3">
         <v>131700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>133300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>123700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>109200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>90600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>99600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>97500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>130900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>106300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2202700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>326900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>163300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>158900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>148300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>166900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>181000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>174000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>245900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>179200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>143300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>167500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>257300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>581700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>199400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>206300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>196800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>195100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>183700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>170700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>178200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>176300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>153800</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2851500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2784800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2774100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2958300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2841900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2940800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3084100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3075000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3022400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3202900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3996500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5505000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3391800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3528200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3414600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3525500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3175200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3674600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3251100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2712900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3244500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3257700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3048900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3460200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3314200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3471600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3361300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3411100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3137400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3174100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3136100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2887600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2841200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2934300</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>28400</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>26400</v>
       </c>
-      <c r="G47" s="3">
-        <v>26000</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>25700</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>24900</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4427,216 +4531,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>216400</v>
+      </c>
+      <c r="E48" s="3">
         <v>230200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>231700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>236500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>245700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>192800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>198700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>203000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>208400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>217200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>228800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>235400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>238200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>901300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>918600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>921200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>940500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>940100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>936800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>952700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>973100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>969500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>965500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1770800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2463800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>912000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>904500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>909600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>908200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>870500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>841300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>837500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>842500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>827700</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1501400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1559500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1562100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1573600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1588800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1547800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1566100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1825300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1831700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1824700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1850400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1985400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2000400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2673700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2696600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2617800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2641700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2251200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2261100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2300400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2328100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2324200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2336500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3052100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2535200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2878900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2889400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2909200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2917900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2818400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2837800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2814200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2838100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2787600</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E52" s="3">
         <v>51300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>49900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23600</v>
       </c>
-      <c r="G52" s="3">
-        <v>23900</v>
-      </c>
       <c r="H52" s="3">
+        <v>49900</v>
+      </c>
+      <c r="I52" s="3">
         <v>22200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>48500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>57300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>56500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>66600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1820300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>67000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>88500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>95700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>40800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>44000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>45000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>33700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>35500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>28300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>26900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>41000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1084300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>38100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>38900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>36300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>20800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>42600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>41500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>40900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>35800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4622300</v>
+      </c>
+      <c r="E54" s="3">
         <v>4625800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4617800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4818400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4726300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4729300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4897400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5147900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5119800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5301300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6126000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7792400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7450700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7170200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7118300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7160200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6798200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6909900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6494000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5999700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6581200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6579700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6377800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8324100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7206200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7300600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7194100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7266200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6984300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6905600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6856700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6580200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6557600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6586400</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>547600</v>
+      </c>
+      <c r="E57" s="3">
         <v>650800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>744100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>556600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>646400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>625700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>683800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>551200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>645600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>736100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>833500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>785300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1070200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1074500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1118100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>688900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>938100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>983800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>354300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>704600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>718500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>847100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>997800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>691300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>870300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>874400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>942700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>682700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>754600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>735500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>786500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>648500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>700300</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1894500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1796600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1845600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1717600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1798400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1737600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1905300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1864000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>290600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>283600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>760900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1034000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>19900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>19100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>22700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>30400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>24300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>26400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>27000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>42100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>39000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>105500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>148200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>13100</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>17700</v>
       </c>
       <c r="AC58" s="3">
         <v>17700</v>
       </c>
       <c r="AD58" s="3">
+        <v>17700</v>
+      </c>
+      <c r="AE58" s="3">
         <v>16800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>12400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>16800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>17700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>38000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>105200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E59" s="3">
         <v>4400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1801400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1891200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2050900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2614300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2374000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1667400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1586100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1507500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1537400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1390000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>998600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1637500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1771000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1758700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1715800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1799600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1920400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1736900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1672100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1668400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1694100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1576200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1509700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1509100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1581300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1558900</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2565500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2585300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2576100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2573700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2478800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2508700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2646200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2666400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2643200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2820400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3547900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4481800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3009300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2756700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2683300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2656000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2250600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2354500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2009300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2018800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2517700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2516200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2668400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2945600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2624800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2624900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2564200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2627900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2389200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2347600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2262900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2333600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2335000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2283900</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E61" s="3">
         <v>64100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>65500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>267900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>272800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>273800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>275900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>283500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>206200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>194700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>190700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>939800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1852700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1850700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1851800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1852800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1853800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1854800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1856900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1860100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1875300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1877600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1403800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2676000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2654300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2657600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2660900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2664300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2667700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2671000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2675200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2360500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2365100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2371800</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E62" s="3">
         <v>15700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>139600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>139300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>146000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>253300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>484800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>499700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>511900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>504100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>528200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>553600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>545100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>549000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>538000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>550100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>553000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1200000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>462900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>456600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>456500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>453900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>442500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>484300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>456800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>455700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>460200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>452900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2667100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2686200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2677100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2875700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2786800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2811200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2950500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3009500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2989000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3154400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3884600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5674900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5346800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5107100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5047000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5012900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4632600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4762900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4411300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4427900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4931000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4943900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4625200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6821600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5742000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5739100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5681600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5746100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5499400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5502900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5394900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5149800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5160300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5108600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6553,32 +6720,32 @@
         <v>612500</v>
       </c>
       <c r="N70" s="3">
+        <v>612500</v>
+      </c>
+      <c r="O70" s="3">
         <v>601600</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>590900</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>580400</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>570000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>559800</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>549800</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>540000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>528200</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>689800</v>
+      </c>
+      <c r="E72" s="3">
         <v>648600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>631300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>631800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>624400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>621200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>619600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>824500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>822900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>796900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>813800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>614600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>625700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>631100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>642500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>641200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>600700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>627800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>592500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>624800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>651000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>655700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>644900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>422900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>392300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>371500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>341100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>295000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>257000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>131300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>111800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>98600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>74100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1342700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1327100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1328200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1330200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1327000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1305600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1334400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1525900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1518300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1534400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1628900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1515900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1513000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1482700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1501300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1587500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1615800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1607000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1554500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1571800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1650200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1635800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1752600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1502500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1464200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1561500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1512500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1520100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1484900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1402700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1430400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1397300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1477800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E81" s="3">
         <v>28400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18500</v>
       </c>
-      <c r="G81" s="3">
-        <v>14300</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3">
         <v>12700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-193800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>198900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>52100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-26900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>30000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-24200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>55600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>77800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>67300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>77500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>93200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>90000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>172800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>62800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>57200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>69200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>45500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>26400</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>23000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>51900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>44700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>92400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>47000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>50600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>46500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>94200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>47700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>50100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>46400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>26100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>66100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>67100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>65600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>66900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>70300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>69400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>66200</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>64500</v>
       </c>
       <c r="AH83" s="3">
         <v>64500</v>
       </c>
       <c r="AI83" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>64700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E89" s="3">
         <v>121100</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>100200</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>73600</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>96100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-125300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-326900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-86100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>73300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>59800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>295700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>164500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-47500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>163000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>268900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-49200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>94200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>130300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>223800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>93700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>164000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>199100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>234400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>152300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>100900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>114000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>231900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>142000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>87100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13100</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-12900</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-12900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-12000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-32600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-46700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-29600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-34000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-49200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-46100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-32300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-48600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-31300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-34700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-74400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-73200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-161500</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-81300</v>
+      </c>
+      <c r="E94" s="3">
         <v>4500</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-39700</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>12400</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-5600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>164400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>109800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1873200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-258500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-803600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-89300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-325700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-79200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-590200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-222300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>485900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>116700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-47700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-98400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-150300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-147100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-68600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-91500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-109600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-134400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-99800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8877,55 +9110,58 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-49000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-24500</v>
       </c>
       <c r="W96" s="3">
         <v>-24500</v>
       </c>
       <c r="X96" s="3">
-        <v>0</v>
+        <v>-24500</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-93300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-46500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-47100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-47200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-43300</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-43900</v>
       </c>
       <c r="AG96" s="3">
         <v>-43900</v>
       </c>
       <c r="AH96" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-43700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-40100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-40000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-97800</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-63600</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>-116500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-81900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-618100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-911100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>298700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>273100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>50600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-113300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-88700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>105900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>368800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-279900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-197200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-23300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>247100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-51700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-48200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-115700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-41800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-34500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-110900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>174200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-136400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-59300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-13900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6200</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-21300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-21300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-6100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>12700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-17300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-23700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-4600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E102" s="3">
         <v>32000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-8000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-120400</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-24900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-654900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>629100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-42900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-455600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-136900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-519100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>312900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>457600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-153400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>29000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>275200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>26800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-74800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-113000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>87200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>39100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>14800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-115600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-98000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>342300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-121300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>8400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>KAR</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>460100</v>
+      </c>
+      <c r="E8" s="3">
         <v>492000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>448400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>431800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>429900</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3">
         <v>416300</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" s="3">
-        <v>416300</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>416900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>420600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>372800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>393000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>753600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>369400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>357700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>347100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>745800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>369800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>529600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>593600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1064500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>645500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>671300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>701900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>719100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>689600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>593800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>612400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>956600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>950500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>890400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>843000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>858000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>866600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>859500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>789600</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E9" s="3">
         <v>244500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>252000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>245900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>213900</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3">
         <v>216000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>222600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>224200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>202000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>209600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>422700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>210800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>194200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>185700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>412600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>203800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>325400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>329700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>629700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>394600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>394900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>410900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>417400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>393900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>332300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>330700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>531300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>535000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>525100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>479200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>481700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>501200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>534100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>459500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E10" s="3">
         <v>247500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>196400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>185900</v>
       </c>
-      <c r="G10" s="3">
-        <v>202400</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="H10" s="3">
+        <v>216000</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3">
         <v>200300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>194300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>196400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>170800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>183400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>330900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>158600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>163500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>161400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>333200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>166000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>204200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>263900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>434800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>250900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>276400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>291000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>301700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>295700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>261500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>281700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>425300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>415500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>365300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>363800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>376300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>365400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>325400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>330100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,17 +1397,20 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-20400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1400,65 +1420,65 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>233000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7700</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-44400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>15700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>11200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>29800</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2200</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1466,136 +1486,142 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>27500</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>1400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E15" s="3">
         <v>23000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>23800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>24300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>25300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>26400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>26800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>23000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>24000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>24300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>51900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>26000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>28200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>27400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>54300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>26900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>50600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>46500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>94200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>47700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>50100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>46400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>47900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>44300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>42600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>41400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>66900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>70300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>69400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>66200</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>64500</v>
       </c>
       <c r="AI15" s="3">
         <v>64500</v>
       </c>
       <c r="AJ15" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AK15" s="3">
         <v>64700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>380800</v>
+      </c>
+      <c r="E17" s="3">
         <v>404700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>375200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>376000</v>
       </c>
-      <c r="G17" s="3">
-        <v>346900</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="H17" s="3">
+        <v>360500</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3">
         <v>349800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>360600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>355200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>285300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>352300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>725300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>355700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>280200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>322300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>696300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>349200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>515700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>507200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1028400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>604700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>609700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>618400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>628500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>613400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>523600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>526800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>781000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>792700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>767000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>701100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>728300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>723100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>749000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>666300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E18" s="3">
         <v>87300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>73200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>55800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>69400</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3">
         <v>66500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>56300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>65400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>87500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>40700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>77500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>24800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>49500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>86400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>36100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>40800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>61600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>83500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>90600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>76200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>70200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>85600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>175600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>157800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>123400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>141900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>129700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>143500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>110500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>123300</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1916,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E20" s="3">
         <v>129300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-52400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>50100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>60900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>23000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1100</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-19000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>100600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>79700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>93200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>25300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>91700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>85500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>92400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>119200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>63800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>75000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>38500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>53300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>42700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>153900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>108400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>60600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>134000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>131000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>90500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>114200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>131900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>139200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>122100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>111500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>130200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>196400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>232900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>215800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>208300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>195300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>208000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>174900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E22" s="3">
         <v>-90600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>37400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>39700</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
         <v>39400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>38800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>38300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>35400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>32300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>51500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>32000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>31900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>61800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>30800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>30500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>29500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>68900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>38000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>39500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>37900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>55200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>56000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>52000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>49200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>49900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>46200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>43300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>41600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>39700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>40200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>38000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>36300</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E23" s="3">
         <v>69000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>41500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29200</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3">
         <v>25400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-213100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>59800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>37800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>50700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>58000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-32100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>47600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>36100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>16900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>39600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>128400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>116400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>103100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>100500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>91100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>103300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>72200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>86200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E24" s="3">
         <v>16700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10700</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3">
         <v>12700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-19300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-14600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>26900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>24500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>10900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>8700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>35200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>26400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>21900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>37700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>33900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>34100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>26700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E26" s="3">
         <v>52300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>28400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18500</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3">
         <v>12700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-193800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>41900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>26200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>47100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-29500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>34400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>27400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>30900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>93200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>90000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>81200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>62800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>57200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>69200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>45500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E27" s="3">
         <v>30900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5600</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-204900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-37300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>12900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-26900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>30000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-24200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>34400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>27400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>30900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>93200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>90000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>81200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>62800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>57200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>69200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>45500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2876,32 +2937,32 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-4800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-6300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>223700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>8100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>25900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>51500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>24700</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
@@ -2912,35 +2973,35 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>4500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>28200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>62500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>52200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>46600</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>91600</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-129300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>52400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-50100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-60900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-23000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E33" s="3">
         <v>52300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>28400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18500</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3">
         <v>12700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-193800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>198900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>52100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>37600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-26900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>30000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-24200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>55600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>77800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>67300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>77500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>93200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>90000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>172800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>62800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>57200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>69200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>45500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E35" s="3">
         <v>52300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>28400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18500</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3">
         <v>12700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-193800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>198900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>52100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>37600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-26900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>30000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-24200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>55600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>77800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>67300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>77500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>93200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>90000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>172800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>62800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>57200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>69200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>45500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>220500</v>
+      </c>
+      <c r="E41" s="3">
         <v>143000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>132100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>60900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>105200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>93500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>110300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>242400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>219600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>225700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>148700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>804400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>134200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>177600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>631900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>621600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>759000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>752100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1276700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>968500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>293100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>507600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>508600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>233000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>265600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>277100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>455100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>369800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>330800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>317200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>432100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>530400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>188000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>201800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>323100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,115 +4089,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2678600</v>
+      </c>
+      <c r="E43" s="3">
         <v>2570900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2492500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2512200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2683700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2573800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2698100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2712000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2725700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2665800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2953500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3085800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3168100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2887300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2733000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2634100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2618200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2256200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2216900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2108600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2173900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2557700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2605800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2648400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2937300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2455400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2817100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2785200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2883500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2625100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2558300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2435000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2521400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2463100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2457400</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,252 +4309,261 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>110500</v>
+      </c>
+      <c r="E45" s="3">
         <v>96900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>131700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>133300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>123700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>109200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>90600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>99600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>97500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>130900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>106300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2202700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>326900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>163300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>158900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>148300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>166900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>181000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>174000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>245900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>179200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>143300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>167500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>257300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>581700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>199400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>206300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>196800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>195100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>183700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>170700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>178200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>176300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>153800</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3045600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2851500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2784800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2774100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2958300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2841900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2940800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3084100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3075000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3022400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3202900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3996500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5505000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3391800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3528200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3414600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3525500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3175200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3674600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3251100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2712900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3244500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3257700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3048900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3460200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3314200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3471600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3361300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3411100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3137400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3174100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3136100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2887600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2841200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2934300</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E47" s="3">
         <v>28400</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>26400</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>25700</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>24900</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4534,222 +4639,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>211700</v>
+      </c>
+      <c r="E48" s="3">
         <v>216400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>230200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>231700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>236500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>245700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>192800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>198700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>203000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>208400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>217200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>228800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>235400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>238200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>901300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>918600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>921200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>940500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>940100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>936800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>952700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>973100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>969500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>965500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1770800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2463800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>912000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>904500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>909600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>908200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>870500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>841300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>837500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>842500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>827700</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1497400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1501400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1559500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1562100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1573600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1588800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1547800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1566100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1825300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1831700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1824700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1850400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1985400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2000400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2673700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2696600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2617800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2641700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2251200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2261100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2300400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2328100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2324200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2336500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3052100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2535200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2878900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2889400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2909200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2917900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2818400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2837800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2814200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2838100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2787600</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E52" s="3">
         <v>24600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>51300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>49900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>49900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>48500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>57300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>56500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>66600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1820300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>67000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>88500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>95700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>40800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>44000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>45000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>33700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>35500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>28300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>26900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>41000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1084300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>38100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>38900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>36300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>20800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>42600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>41500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>40900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>35800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4806400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4622300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4625800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4617800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4818400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4726300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4729300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4897400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5147900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5119800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5301300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6126000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7792400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7450700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7170200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7118300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7160200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6798200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6909900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6494000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5999700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6581200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6579700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6377800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8324100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7206200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7300600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7194100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7266200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6984300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6905600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6856700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6580200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6557600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6586400</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>710400</v>
+      </c>
+      <c r="E57" s="3">
         <v>547600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>650800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>744100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>556600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>646400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>625700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>683800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>551200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>645600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>736100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>833500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>785300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1070200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1074500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1118100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>688900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>938100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>983800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>354300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>704600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>718500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>847100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>997800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>691300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>870300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>874400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>942700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>682700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>754600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>735500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>786500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>648500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>700300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1885300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1894500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1796600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1845600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1717600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1798400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1737600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1905300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1864000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>290600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>283600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>760900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1034000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>19900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>19100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>22700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>30400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>24300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>26900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>27000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>42100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>39000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>105500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>148200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>13100</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>17700</v>
       </c>
       <c r="AD58" s="3">
         <v>17700</v>
       </c>
       <c r="AE58" s="3">
+        <v>17700</v>
+      </c>
+      <c r="AF58" s="3">
         <v>16800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>12400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>16800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>17700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>38000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>105200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E59" s="3">
         <v>10600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1801400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1891200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2050900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2614300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2374000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1667400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1586100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1507500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1537400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1390000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>998600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1637500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1771000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1758700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1715800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1799600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1920400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1736900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1672100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1668400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1694100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1576200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1509700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1509100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1581300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1558900</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2720700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2565500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2585300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2576100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2573700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2478800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2508700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2646200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2666400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2643200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2820400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3547900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4481800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3009300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2756700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2683300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2656000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2250600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2354500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2009300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2018800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2517700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2516200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2668400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2945600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2624800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2624900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2564200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2627900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2389200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2347600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2262900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2333600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2335000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2283900</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E61" s="3">
         <v>60400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>64100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>65500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>267900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>272800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>273800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>275900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>283500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>206200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>194700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>190700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>939800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1852700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1850700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1851800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1852800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1853800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1854800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1856900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1860100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1875300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1877600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1403800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2676000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2654300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2657600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2660900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2664300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2667700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2671000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2675200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2360500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2365100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2371800</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E62" s="3">
         <v>16800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>139600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>139300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>146000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>253300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>484800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>499700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>511900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>504100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>528200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>553600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>545100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>549000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>538000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>550100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>553000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1200000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>462900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>456600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>456500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>453900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>442500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>484300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>456800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>455700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>460200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>452900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2821500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2667100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2686200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2677100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2875700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2786800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2811200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2950500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3009500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2989000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3154400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3884600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5674900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5346800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5107100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5047000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5012900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4632600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4762900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4411300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4427900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4931000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4943900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4625200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6821600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5742000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5739100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5681600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5746100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5499400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5502900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5394900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5149800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5160300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5108600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6723,32 +6891,32 @@
         <v>612500</v>
       </c>
       <c r="O70" s="3">
+        <v>612500</v>
+      </c>
+      <c r="P70" s="3">
         <v>601600</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>590900</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>580400</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>570000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>559800</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>549800</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>540000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>528200</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>715600</v>
+      </c>
+      <c r="E72" s="3">
         <v>689800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>648600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>631300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>631800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>624400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>621200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>619600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>824500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>822900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>796900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>813800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>614600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>625700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>631100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>642500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>641200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>600700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>627800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>592500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>624800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>651000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>655700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>644900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>422900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>392300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>371500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>341100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>295000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>257000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>131300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>111800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>98600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>74100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1372400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1342700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1327100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1328200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1330200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1327000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1305600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1334400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1525900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1518300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1534400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1628900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1515900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1482700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1501300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1587500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1615800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1607000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1554500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1571800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1650200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1635800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1752600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1502500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1464200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1561500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1512500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1520100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1484900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1402700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1430400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1397300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1477800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E81" s="3">
         <v>52300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>28400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18500</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3">
         <v>12700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-193800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>198900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>52100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>37600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-26900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>30000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-24200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>55600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>77800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>67300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>77500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>93200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>90000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>172800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>62800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>57200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>69200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>45500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>26400</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
         <v>23000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>51900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>44700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>92400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>47000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>50600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>46500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>94200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>47700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>50100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>46400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>26100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>66100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>67100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>65600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>66900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>70300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>69400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>66200</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>64500</v>
       </c>
       <c r="AI83" s="3">
         <v>64500</v>
       </c>
       <c r="AJ83" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AK83" s="3">
         <v>64700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E89" s="3">
         <v>32700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>121100</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>100200</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
         <v>73600</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>96100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-125300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-326900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-86100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>73300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>59800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>295700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>164500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-47500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>163000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>268900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-49200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>94200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>130300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>223800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>93700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>164000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>199100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>234400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>152300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>100900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>114000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>231900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>142000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>87100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>-12900</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-12900</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-12000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-32600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-46700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-29600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-49200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-46100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-32300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-48600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-31300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-34700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-74400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-73200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-161500</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-81300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4500</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3">
         <v>-39700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
         <v>12400</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-5600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>164400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>109800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1873200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-258500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-803600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-89300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-325700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-79200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-590200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-222300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>485900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>116700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-47700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-98400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-150300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-147100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-68600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-91500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-109600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-134400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-99800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9113,55 +9347,58 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-49000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-24500</v>
       </c>
       <c r="X96" s="3">
         <v>-24500</v>
       </c>
       <c r="Y96" s="3">
-        <v>0</v>
+        <v>-24500</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-93300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-46500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-47100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-47200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-43300</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-43900</v>
       </c>
       <c r="AH96" s="3">
         <v>-43900</v>
       </c>
       <c r="AI96" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-43700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-40100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-40000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E100" s="3">
         <v>90400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-97800</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>-63600</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200200</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-116500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-81900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-618100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-911100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>298700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>273100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>50600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-113300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-88700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>105900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>368800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-279900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-197200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-23300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>247100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-51700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-18300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-48200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-115700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-41800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-34500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-110900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>174200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-136400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-59300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-13900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
         <v>-6200</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-21300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-21300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>6400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>12700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-17300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-23700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-15500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>8500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>6200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E102" s="3">
         <v>23100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-8000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-120400</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-24900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-654900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>629100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-42900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-455600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-136900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-519100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>312900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>457600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-153400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>29000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>275200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>26800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-74800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-113000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>87200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>39100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>14800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-115600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-98000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>342300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-121300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>8400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>KAR</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>481700</v>
+      </c>
+      <c r="E8" s="3">
         <v>460100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>492000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>448400</v>
       </c>
-      <c r="G8" s="3">
-        <v>431800</v>
-      </c>
       <c r="H8" s="3">
+        <v>443800</v>
+      </c>
+      <c r="I8" s="3">
         <v>429900</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>416300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>416900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>420600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>372800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>393000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>753600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>369400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>357700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>347100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>745800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>369800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>529600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>593600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1064500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>645500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>671300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>701900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>719100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>689600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>593800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>612400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>956600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>950500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>890400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>843000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>858000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>866600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>859500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>789600</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>254400</v>
+      </c>
+      <c r="E9" s="3">
         <v>241600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>244500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>252000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>245900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>213900</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>216000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>222600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>224200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>202000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>209600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>422700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>210800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>194200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>185700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>412600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>203800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>325400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>329700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>629700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>394600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>394900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>410900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>417400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>393900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>332300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>330700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>531300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>535000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>525100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>479200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>481700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>501200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>534100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>459500</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>227300</v>
+      </c>
+      <c r="E10" s="3">
         <v>218500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>247500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>196400</v>
       </c>
-      <c r="G10" s="3">
-        <v>185900</v>
-      </c>
       <c r="H10" s="3">
+        <v>197900</v>
+      </c>
+      <c r="I10" s="3">
         <v>216000</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>200300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>194300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>196400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>170800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>183400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>330900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>158600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>163500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>161400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>333200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>166000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>204200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>263900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>434800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>250900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>276400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>291000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>301700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>295700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>261500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>281700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>425300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>415500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>365300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>363800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>376300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>365400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>325400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>330100</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,20 +1417,23 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-20400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1423,65 +1443,65 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>233000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7700</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-44400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>15700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>11200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>29800</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>2200</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1489,139 +1509,145 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>27500</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>1400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E15" s="3">
         <v>22700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>23000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>23800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>24100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>26400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>26800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>23000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>24000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>24300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>51900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>26000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>28200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>27400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>54300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>26900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>50600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>46500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>94200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>47700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>50100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>46400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>47900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>44300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>42600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>41400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>66900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>70300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>69400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>66200</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>64500</v>
       </c>
       <c r="AJ15" s="3">
         <v>64500</v>
       </c>
       <c r="AK15" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AL15" s="3">
         <v>64700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400400</v>
+      </c>
+      <c r="E17" s="3">
         <v>380800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>404700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>375200</v>
       </c>
-      <c r="G17" s="3">
-        <v>376000</v>
-      </c>
       <c r="H17" s="3">
+        <v>388000</v>
+      </c>
+      <c r="I17" s="3">
         <v>360500</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>349800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>360600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>355200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>285300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>352300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>725300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>355700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>280200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>322300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>696300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>349200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>515700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>507200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1028400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>604700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>609700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>618400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>628500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>613400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>523600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>526800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>781000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>792700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>767000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>701100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>728300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>723100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>749000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>666300</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E18" s="3">
         <v>79300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>87300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>73200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>55800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>69400</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>66500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>56300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>65400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>87500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>77500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>49500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>86400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>36100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>40800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>61600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>83500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>90600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>76200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>70200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>85600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>175600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>157800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>123400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>141900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>129700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>143500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>110500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>123300</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,558 +1950,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5000</v>
       </c>
-      <c r="E20" s="3">
-        <v>129300</v>
-      </c>
       <c r="F20" s="3">
+        <v>5800</v>
+      </c>
+      <c r="G20" s="3">
         <v>-3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-52400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>50100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>60900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>23000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E21" s="3">
         <v>107000</v>
       </c>
-      <c r="E21" s="3">
-        <v>-19000</v>
-      </c>
       <c r="F21" s="3">
+        <v>104500</v>
+      </c>
+      <c r="G21" s="3">
         <v>100600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>79700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>93200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>25300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>91700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>85500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>92400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>119200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>63800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>75000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>38500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>53300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>42700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>153900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>108400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>60600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>134000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>131000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>90500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>114200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>131900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>139200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>122100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>111500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>130200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>196400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>232900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>215800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>208300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>195300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>208000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>174900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E22" s="3">
         <v>31600</v>
       </c>
-      <c r="E22" s="3">
-        <v>-90600</v>
-      </c>
       <c r="F22" s="3">
+        <v>32900</v>
+      </c>
+      <c r="G22" s="3">
         <v>35300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>37400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>39700</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>39400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>38800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>38300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>35400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>32300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>51500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>25600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>32000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>31900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>61800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>30800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>30500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>29500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>68900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>38000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>39500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>37900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>55200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>56000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>52000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>49200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>49900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>46200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>43300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>41600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>39700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>40200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>38000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>36300</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E23" s="3">
         <v>52700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>69000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>41500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>29200</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>25400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-213100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>59800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>37800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>50700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>58000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-32100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>47600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>36100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>16900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>39600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>128400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>116400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>103100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>91100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>103300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>72200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>86200</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E24" s="3">
         <v>15800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10700</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>12700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-19300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-14600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-22100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>26900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>24500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>8700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>35200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>26400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>21900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>37700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>33900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>34100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>26700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E26" s="3">
         <v>36900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>52300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>28400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18500</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>12700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-193800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>41900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>26200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>47100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-29500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>34400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>27400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>15100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>30900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>93200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>90000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>81200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>62800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>57200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>69200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>45500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E27" s="3">
         <v>19400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>30900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5600</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>1200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-204900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-37300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-26900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-24200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>34400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>27400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>15100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>30900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>93200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>90000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>81200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>62800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>57200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>69200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>45500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2940,32 +3001,32 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-4800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-6300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>223700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>8100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-10100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>25900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>51500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>24700</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -2976,35 +3037,35 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>4500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>900</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>28200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>62500</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>52200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>46600</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>91600</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E32" s="3">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
-        <v>-129300</v>
-      </c>
       <c r="F32" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="G32" s="3">
         <v>3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>52400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-50100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-60900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-23000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E33" s="3">
         <v>36900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>52300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>28400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18500</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>12700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-193800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>198900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>52100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>37600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-26900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>30000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-24200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>55600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>77800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>67300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>77500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>93200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>90000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>172800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>62800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>57200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>69200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>45500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E35" s="3">
         <v>36900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>52300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>28400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18500</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>12700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-193800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>198900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>52100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>37600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-26900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>30000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-24200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>55600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>77800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>67300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>77500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>93200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>90000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>172800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>62800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>57200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>69200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>45500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>119100</v>
+      </c>
+      <c r="E41" s="3">
         <v>220500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>143000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>132100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>60900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>105200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>93500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>110300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>242400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>219600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>225700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>148700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>804400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>134200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>177600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>631900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>621600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>759000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>752100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1276700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>968500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>293100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>507600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>508600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>233000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>265600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>277100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>455100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>369800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>330800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>317200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>432100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>530400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>188000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>201800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>323100</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,118 +4182,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2661700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2678600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2570900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2492500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2512200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2683700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2573800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2698100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2712000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2725700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2665800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2953500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3085800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3168100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2887300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2733000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2634100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2618200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2256200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2216900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2108600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2173900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2557700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2605800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2648400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2937300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2455400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2817100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2785200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2883500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2625100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2558300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2435000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2521400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2463100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2457400</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,261 +4408,270 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>94300</v>
+      </c>
+      <c r="E45" s="3">
         <v>110500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>96900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>131700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>133300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>123700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>109200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>90600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>99600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>97500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>130900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>106300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2202700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>326900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>163300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>158900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>148300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>166900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>181000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>174000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>245900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>179200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>143300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>167500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>257300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>581700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>199400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>206300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>196800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>195100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>183700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>170700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>178200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>176300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>153800</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2904800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3045600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2851500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2784800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2774100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2958300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2841900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2940800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3084100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3075000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3022400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3202900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3996500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5505000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3391800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3528200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3414600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3525500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3175200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3674600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3251100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2712900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3244500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3257700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3048900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3460200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3314200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3471600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3361300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3411100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3137400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3174100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3136100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2887600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2841200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2934300</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E47" s="3">
         <v>29000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28400</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>26400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>25700</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>24900</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4642,228 +4747,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>167100</v>
+      </c>
+      <c r="E48" s="3">
         <v>211700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>216400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>230200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>231700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>236500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>245700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>192800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>198700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>203000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>208400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>217200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>228800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>235400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>238200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>901300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>918600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>921200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>940500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>940100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>936800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>952700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>973100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>969500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>965500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1770800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2463800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>912000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>904500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>909600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>908200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>870500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>841300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>837500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>842500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>827700</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1507300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1497400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1501400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1559500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1562100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1573600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1588800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1547800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1566100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1825300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1831700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1824700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1850400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1985400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2000400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2673700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2696600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2617800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2641700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2251200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2261100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2300400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2328100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2324200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2336500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3052100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2535200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2878900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2889400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2909200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2917900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2818400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2837800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2814200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2838100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2787600</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E52" s="3">
         <v>22700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>51300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>49900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>49900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>48500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>57300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>56500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>50300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>66600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1820300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>67000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>88500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>95700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>40800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>44000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>45000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>33700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>35500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>28300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>26900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>41000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1084300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>38100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>38900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>36300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>20800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>42600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>41500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>40900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>35800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4638300</v>
+      </c>
+      <c r="E54" s="3">
         <v>4806400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4622300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4625800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4617800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4818400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4726300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4729300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4897400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5147900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5119800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5301300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6126000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7792400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7450700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7170200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7118300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7160200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6798200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6909900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6494000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5999700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6581200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6579700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6377800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8324100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7206200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7300600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7194100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7266200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6984300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6905600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6856700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6580200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6557600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>6586400</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>645000</v>
+      </c>
+      <c r="E57" s="3">
         <v>710400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>547600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>650800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>744100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>556600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>646400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>625700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>683800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>551200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>645600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>736100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>833500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>785300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1070200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1074500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1118100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>688900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>938100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>983800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>354300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>704600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>718500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>847100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>997800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>691300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>870300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>874400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>942700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>682700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>754600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>735500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>786500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>648500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>700300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1724800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1885300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1894500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1796600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1845600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1717600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1798400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1737600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1905300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1864000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>290600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>283600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>760900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1034000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>19900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>19100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>22700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>30400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>24300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>26400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>26900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>27000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>42100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>39000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>105500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>148200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>13100</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>17700</v>
       </c>
       <c r="AE58" s="3">
         <v>17700</v>
       </c>
       <c r="AF58" s="3">
+        <v>17700</v>
+      </c>
+      <c r="AG58" s="3">
         <v>16800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>12400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>16800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>17700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>38000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>105200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E59" s="3">
         <v>3800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1801400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1891200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2050900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2614300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2374000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1667400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1586100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1507500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1537400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1390000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>998600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1637500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1771000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1758700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1715800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1799600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1920400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1736900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1672100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1668400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1694100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1576200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1509700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1509100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1581300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1558900</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2509400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2720700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2565500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2585300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2576100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2573700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2478800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2508700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2646200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2666400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2643200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2820400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3547900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4481800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3009300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2756700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2683300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2656000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2250600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2354500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2009300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2018800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2517700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2516200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2668400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2945600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2624800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2624900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2564200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2627900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2389200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2347600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2262900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2333600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2335000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2283900</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E61" s="3">
         <v>58200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>60400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>64100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>65500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>267900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>272800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>273800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>275900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>283500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>206200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>194700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>190700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>939800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1852700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1850700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1851800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1852800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1853800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1854800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1856900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1860100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1875300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1877600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1403800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2676000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2654300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2657600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2660900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2664300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2667700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2671000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2675200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2360500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2365100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2371800</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E62" s="3">
         <v>17400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>139600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>139300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>146000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>253300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>484800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>499700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>511900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>504100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>528200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>553600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>545100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>549000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>538000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>550100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>553000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1200000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>462900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>456600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>456500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>453900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>442500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>484300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>456800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>455700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>460200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>452900</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2610200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2821500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2667100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2686200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2677100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2875700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2786800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2811200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2950500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3009500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2989000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3154400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3884600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5674900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5346800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5107100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5047000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5012900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4632600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4762900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4411300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4427900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4931000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4943900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4625200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6821600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5742000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5739100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5681600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5746100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5499400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5502900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5394900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5149800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5160300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5108600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6894,32 +7062,32 @@
         <v>612500</v>
       </c>
       <c r="P70" s="3">
+        <v>612500</v>
+      </c>
+      <c r="Q70" s="3">
         <v>601600</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>590900</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>580400</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>570000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>559800</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>549800</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>540000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>528200</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>737900</v>
+      </c>
+      <c r="E72" s="3">
         <v>715600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>689800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>648600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>631300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>631800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>624400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>621200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>619600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>824500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>822900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>796900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>813800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>614600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>625700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>631100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>642500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>641200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>600700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>627800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>592500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>624800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>651000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>655700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>644900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>422900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>392300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>371500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>341100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>295000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>257000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>131300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>111800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>98600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>74100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1415600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1372400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1342700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1327100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1328200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1330200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1327000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1305600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1334400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1525900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1518300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1534400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1628900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1515900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1513000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1482700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1501300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1587500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1615800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1607000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1554500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1571800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1650200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1635800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1752600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1502500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1464200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1561500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1512500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1520100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1484900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1402700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1430400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1397300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1477800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E81" s="3">
         <v>36900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>52300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>28400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18500</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>12700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-193800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>198900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>52100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>37600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-26900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>30000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-24200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>55600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>77800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>67300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>77500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>93200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>90000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>172800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>62800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>57200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>69200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>45500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>24300</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>26400</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
         <v>23000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>51900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>26000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>45900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>44700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>92400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>47000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>50600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>46500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>94200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>47700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>50100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>46400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>26100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>66100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>67100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>65600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>66900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>70300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>69400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>66200</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>64500</v>
       </c>
       <c r="AJ83" s="3">
         <v>64500</v>
       </c>
       <c r="AK83" s="3">
+        <v>64500</v>
+      </c>
+      <c r="AL83" s="3">
         <v>64700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E89" s="3">
         <v>122600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>121100</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>100200</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>73600</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3">
         <v>96100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-125300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-326900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-86100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>73300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>59800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>295700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>164500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-47500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>163000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>268900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-49200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>94200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>130300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>223800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>93700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>164000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>199100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>234400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>152300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>100900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>114000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>231900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>142000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>87100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13100</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-12900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-12900</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-12000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-18000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-32600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-46700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-29600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-34000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-49200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-46100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-32300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-48600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-34700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-74400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-73200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-161500</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-81300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4500</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-39700</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>12400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M94" s="3">
         <v>-5600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>164400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>109800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1873200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-258500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-803600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-89300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-325700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-79200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-590200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-222300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>485900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>116700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-47700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-98400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-150300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-147100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-68600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-91500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-109600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-134400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-99800</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9350,55 +9584,58 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-49000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-24500</v>
       </c>
       <c r="Y96" s="3">
         <v>-24500</v>
       </c>
       <c r="Z96" s="3">
-        <v>0</v>
+        <v>-24500</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-93300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-46500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-47100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-47200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-43300</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-43900</v>
       </c>
       <c r="AI96" s="3">
         <v>-43900</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-43700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-40100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-40000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>90400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-97800</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-63600</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" s="3">
         <v>-116500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-81900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-618100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-911100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>298700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>273100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>50600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-113300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-88700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>105900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>368800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-279900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-197200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>247100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-51700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-18300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-48200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-115700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-41800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-34500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-110900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>174200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-136400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-59300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-13900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4900</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
         <v>-6200</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-21300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-21300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>6400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>12700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-17300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-23700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-15500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>8500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-4600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-107700</v>
+      </c>
+      <c r="E102" s="3">
         <v>72800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>23100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-8000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-120400</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-24900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-654900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>629100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-455600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-136900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-519100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>312900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>457600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-153400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>29000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>275200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>26800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-74800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-113000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>87200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>39100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>14800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-115600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-98000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>342300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-121300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>8400</v>
       </c>
     </row>
